--- a/data/new_records.xlsx
+++ b/data/new_records.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P70"/>
+  <dimension ref="A1:P105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,17 +501,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ВАДИС ООД</t>
+          <t>НЮ ИЛЕКТРИК ПАУЪР ЕООД</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>122092155</t>
+          <t>205905885</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Вадис - Пазарджик"</t>
+          <t>ФтЕЦ "Мокрище"</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -526,22 +526,22 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Пазарджик</t>
+          <t>Мокрище</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>55155</t>
+          <t>48876</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>27.06.2012</t>
+          <t>29.11.2011</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -554,60 +554,64 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>ff6080c5fb233dff83662eea22ef48ab68eb5068d73954fe3e15e09f7034b182</t>
+          <t>06de05a2b321f77b8bb9930b2b3a146876c4310c9960feddba33e8e55c4a9b6f</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Йорданка Велеславова Тачева</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
+          <t>НЮ ИЛЕКТРИК ПАУЪР ЕООД</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>205905885</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Балкански"</t>
+          <t>ФтЕЦ "Еспе Енерджи"</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Разград</t>
+          <t>Плевен</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Разград</t>
+          <t>Гулянци</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Балкански</t>
+          <t>Милковица</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>48204</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>24.10.2017</t>
+          <t>28.06.2012</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -620,64 +624,64 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0d7beb891aee4a9095d1ec2494dfa34112c9967ec606ab52b160e4d05a0e1b78</t>
+          <t>d31326de31ae2f3b5a1ae1375637dd84d1559ff845a0181d428edd7480a86bcc</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ЕЛИТ ЕНЕРДЖИ 2025 ЕООД</t>
+          <t>ЕТ ЕЛМИРА ГЕОРГИЕВА - ИЧИ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>208627715</t>
+          <t>121230653</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Елит газ - Вилна зона 1"</t>
+          <t>ФтЕЦ "Долна баня"</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Сливен</t>
+          <t>София-Област</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Сливен</t>
+          <t>Долна баня</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Сливен</t>
+          <t>Долна баня</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>67338</t>
+          <t>22006</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.18424</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>01.10.2019</t>
+          <t>12.10.2012</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -690,64 +694,64 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>5587a85e31bc56e19d106928db16ec79a891569637366ed2e8ed1f2206470f0f</t>
+          <t>04d42ac29e2eee46ff0e480fb1433dd8acaceb5056fc8c65a18addabe8913300</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ЕЛИТ ЕНЕРДЖИ 2025 ЕООД</t>
+          <t>БОСОЛАР ЕООД</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>208627715</t>
+          <t>200622591</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Елит газ - Вилна зона 2"</t>
+          <t>ФтЕЦ "Енвиво 4 - Зетьово"</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Сливен</t>
+          <t>Стара Загора</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Сливен</t>
+          <t>Чирпан</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Сливен</t>
+          <t>Зетьово</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>67338</t>
+          <t>30819</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.19941</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>23.07.2020</t>
+          <t>08.06.2012</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -760,54 +764,54 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>824ef70446b3a81159905d4a9b7d2d3d3a96b49c7f493f155f479b1755ec796f</t>
+          <t>9196e3b3e64d2ffab4f71b7b741c1327da356dc26c75bc6c8be271e34b80e912</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ПЕТРОСОЛАР ЕООД</t>
+          <t>МИЗАН ЕООД</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>206908724</t>
+          <t>201389300</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Петро Солар - Жребино 3"</t>
+          <t>ФтЕЦ "Мизан - Крумовград"</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Ямбол</t>
+          <t>Кърджали</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Елхово</t>
+          <t>Крумовград</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Жребино</t>
+          <t>Крумовград</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>29516</t>
+          <t>39970</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -817,7 +821,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>14.01.2021</t>
+          <t>21.12.2013</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -830,64 +834,64 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>3af3963ed056c975d5c8efdf8c7ceded9e297754f7c1165c05cdb48e56b02e4a</t>
+          <t>b1448f1e135c375ec24b151327f491de60e7be0edc42d812d818e7f52503e870</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>БОЯНОВ МАШИНИ ЕООД</t>
+          <t>СТЕФАНОВИ ООД</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>128529829</t>
+          <t>102860238</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Боянов Машини - Ямбол"</t>
+          <t>ВтЕЦ "Стефанови 2 - Зетьово"</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Ямбол</t>
+          <t>Бургас</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ямбол</t>
+          <t>Айтос</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ямбол</t>
+          <t>Зетьово</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>87374</t>
+          <t>30805</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>15.07.2020</t>
+          <t>15.09.2014</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -895,59 +899,59 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Слънчева енергия</t>
+          <t>Вятърна енергия</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>845081a9346eac402a3f71bd50cfc1ddaa71230a4874b41dc4de9f869ae7f109</t>
+          <t>1e247143cc5f9ee754323c49c2b1fc17c71f9ead778eb12b849e52b24bb437fd</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>РИЦ 3 ЕООД</t>
+          <t>СТУДИО МАЯ ЕООД</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>131144747</t>
+          <t>131021997</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Бдин 1А"</t>
+          <t>ФтЕЦ "Студио Мая"</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>София-град</t>
+          <t>Благоевград</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Столична</t>
+          <t>Гърмен</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>София</t>
+          <t>Гърмен</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>68134</t>
+          <t>18366</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -957,7 +961,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>09.07.2021</t>
+          <t>01.10.2015</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -970,60 +974,64 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>ce5615172e441b9a37160c10487a8d1558e383cc21abec2f17745b7516b25066</t>
+          <t>3d615a32783c98cc82f857adb3d84b751aec3af0801298824b9cc743d9fa8c0f</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ДИМИТЪР НИКОЛОВ БОЯДЖИЕВ</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
+          <t>ЦМ Еделвайс комфорт ООД</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>205450479</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Димитър Бояджиев - Горно Вършило"</t>
+          <t>ФтЕЦ "Иваново - 1"</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Пазарджик</t>
+          <t>Русе</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Септември</t>
+          <t>Иваново</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Горно вършило</t>
+          <t>Иваново</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>16732</t>
+          <t>32095</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.01488</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>07.04.2021</t>
+          <t>28.09.2020</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -1036,64 +1044,64 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>a3c4b35c9b5cd7e53134e9a8038740d65a2a088eb7ae16eae6425712f939855b</t>
+          <t>2c0d71f4b52ef2fe2b6b2a223562564cb569febdf0a434bb0f03cbaad55ad7d5</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ЕЛИТ ЕНЕРДЖИ 2025 ЕООД</t>
+          <t>ЗП ТОНЧО НИКОЛОВ ДРАГНЕВ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>208627715</t>
+          <t>102907086</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Елит Газ - Коньово 1"</t>
+          <t>ФтЕЦ "Тончо Драгнев - Чубра 2"</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Сливен</t>
+          <t>Бургас</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Нова Загора</t>
+          <t>Сунгурларе</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Коньово</t>
+          <t>Чубра</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>38426</t>
+          <t>81582</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.0297</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>01.07.2021</t>
+          <t>22.07.2021</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -1106,55 +1114,59 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>ed0ed67ba786edd3c09d173791541345bd112007222ffd8ad962b612d44ffbc4</t>
+          <t>d5a955882a9b2dfa3d2bbe3533f3de181305acc276942b4b7952a05d4b8a69cd</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Мирослав Александров Джупанов</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
+          <t>ЗП ТОНЧО НИКОЛОВ ДРАГНЕВ</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>102907086</t>
+        </is>
+      </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Марин Джупанов"</t>
+          <t>ФтЕЦ "Тончо Драгнев - Чубра 3"</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Перник</t>
+          <t>Бургас</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Радомир</t>
+          <t>Сунгурларе</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Дебели лаг</t>
+          <t>Чубра</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20256</t>
+          <t>81582</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.029575</t>
+          <t>0.0297</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1172,64 +1184,64 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>075f416db561aba27ed29d23f18d4717244363ae0a67a59026bb34864df5f046</t>
+          <t>5b5f6acdaec9eaa7e26fa073a1a2eb077bfd3b44ee7f863e6bbb42bab0f84988</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Мирков Агро - 94 ЕООД</t>
+          <t>ЗП ТОНЧО НИКОЛОВ ДРАГНЕВ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>205650833</t>
+          <t>102907086</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Мирков Агро"</t>
+          <t>ФтЕЦ " Драгнев - Славянци 2"</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Плевен</t>
+          <t>Бургас</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Гулянци</t>
+          <t>Сунгурларе</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ленково</t>
+          <t>Славянци</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>43284</t>
+          <t>67115</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.0297</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>02.08.2021</t>
+          <t>29.10.2021</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -1242,60 +1254,64 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>46301850fa42075dc32efd6f5db528cb8b3d3d923ce6d0ca1a5b7c181fb48af2</t>
+          <t>b2c6ddd5cbe361457ede9cfd22a988c7ca73cc8abac5c8e5a462339dd078cebe</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>КРИСТИНА ПАВЛИНОВА ГЕНЧЕВА</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
+          <t>ЗП ТОНЧО НИКОЛОВ ДРАГНЕВ</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>102907086</t>
+        </is>
+      </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ФЕЦ "Стефан Стамболово - Свищов"</t>
+          <t>ФтЕЦ " Драгнев - Славянци 1"</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Велико Търново</t>
+          <t>Бургас</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Полски Тръмбеш</t>
+          <t>Сунгурларе</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Стефан Стамболово</t>
+          <t>Славянци</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>17467</t>
+          <t>67115</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.0292</t>
+          <t>0.0297</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>25.11.2021</t>
+          <t>22.07.2021</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -1308,54 +1324,54 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>5c72ac1a261dcec58b1ae88d6741f4deedaca054a6666e660003972a6f02f1a9</t>
+          <t>d04c59e04c64f22c2cc1f240cae900a5696d21a03662c171aff92c97c9aef2d5</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ЕЛИТ ЕНЕРДЖИ 2025 ЕООД</t>
+          <t>ЗП ТОНЧО НИКОЛОВ ДРАГНЕВ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>208627715</t>
+          <t>102907086</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ФтЕЦ "ТП-ЮГ, ВИ-4, СТ-1"</t>
+          <t>ФтЕЦ "Тончо Драгнев - Чубра 1"</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Сливен</t>
+          <t>Бургас</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Сливен</t>
+          <t>Сунгурларе</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Желю войвода</t>
+          <t>Чубра</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>29194</t>
+          <t>81582</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1365,7 +1381,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>01.03.2022</t>
+          <t>11.03.2021</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -1378,60 +1394,64 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>3dd7a6cb2600fc60c451325ff1091a7e5d1d86aa209e71170e58c645f1c2835c</t>
+          <t>6053e8f88b90ddf28e824d07b963cea5aa1f4a6ea4892befcfab27dd1fcdbdf5</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Матей Петров Матеев</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
+          <t>МИЗАН ЕООД</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>201389300</t>
+        </is>
+      </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Къкрина 5"</t>
+          <t>ФтЕЦ "Мизан - Свирачи"</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Ловеч</t>
+          <t>Хасково</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ловеч</t>
+          <t>Ивайловград</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Къкрина</t>
+          <t>Свирачи</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>40837</t>
+          <t>65704</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.0297</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>04.05.2022</t>
+          <t>22.05.2021</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -1444,54 +1464,54 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>42c6ce49ba1f4121fd25290478dc8612fb2a96233735b5dbca02bf5b6eceaa9c</t>
+          <t>3561dfdaf5a639eb2b771935824e9f1b901ced8067a2878528a33d6a95ce46ea</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ЕЛИТ ЕНЕРДЖИ 2025 ЕООД</t>
+          <t>ХАЙ ТЕК СЕРВИЗ ООД</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>208627715</t>
+          <t>202927894</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Елит Газ - Сливен 1"</t>
+          <t>ФЕЦ ЛЕДЕНИК 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Сливен</t>
+          <t>Велико Търново</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Сливен</t>
+          <t>Велико Търново</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Сливен</t>
+          <t>Велико Търново</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>67338</t>
+          <t>10447</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1501,7 +1521,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>01.04.2022</t>
+          <t>18.01.2022</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -1514,64 +1534,64 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>fc95b6b6297d9b72f398718719090e480efe31c998b6b0680bad3e6cb7d0739e</t>
+          <t>5247510900c59bc6fa10cdb8e90fe75d544c734a07e34245341689ff4802d344</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Бул Инвест 25 ЕООД</t>
+          <t>ТРИ ИНВЕСТ ЕООД</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>208627722</t>
+          <t>119656471</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Елит Газ - Деветинци 3"</t>
+          <t>ФтЕЦ "Ковачевец - 8"</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Бургас</t>
+          <t>Търговище</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Карнобат</t>
+          <t>Попово</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Деветинци</t>
+          <t>Ковачевец</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20448</t>
+          <t>37469</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.02975</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>08.08.2022</t>
+          <t>24.06.2021</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -1584,60 +1604,64 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>cb96aa0967555b7d60d0bf1ae417fcd64aa30088f9244edf24e7a4b5a6d28314</t>
+          <t>9f5512a21e929285084744fca22a27edebb7905e6a2bce378bce54ccd38810ae</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Марийка Крумова Георгиева</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
+          <t>ТРИ ИНВЕСТ ЕООД</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>119656471</t>
+        </is>
+      </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Марийка Георгиева-Каменово"</t>
+          <t>ФтЕЦ "Садина - 9"</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Сливен</t>
+          <t>Търговище</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Нова Загора</t>
+          <t>Попово</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Каменово</t>
+          <t>Садина</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>35907</t>
+          <t>65067</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.02975</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>15.03.2022</t>
+          <t>20.05.2021</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
@@ -1650,71 +1674,67 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>d2de1fd054995c9f410769d26fa16c5d2f67d1a7b7872320680edad74c873be8</t>
+          <t>83e9781dbbd5728a1c9d80de903a4fce15c853d63d1cce66dacf35a8eba636cb</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ИВ ТРЕЙДКОМ ЕООД</t>
+          <t>ТРИ ИНВЕСТ ЕООД</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>206906381</t>
+          <t>119656471</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ФтЕЦ" Ив трейдком 1"</t>
+          <t>ФтЕЦ "Паламарца - 5"</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Плевен</t>
+          <t>Търговище</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Никопол</t>
+          <t>Попово</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Новачене</t>
+          <t>Паламарца</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>51932</t>
+          <t>55213</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.02975</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>27.10.2022</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>28.11.2022</t>
-        </is>
-      </c>
+          <t>24.06.2021</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
@@ -1724,64 +1744,64 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>172c2661cf5a937a93610c3eefaba539785ad766794cb027c11a4b6503353cdc</t>
+          <t>f9934ae8bd537d651f8d92d001e49a328bcbdb6330d86b96585dc3baa4684caa</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>СТЕФАНИ-СТЕФКА БОЖИНОВА ЕООД</t>
+          <t>ТРИ ИНВЕСТ ЕООД</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>106626688</t>
+          <t>119656471</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Стефани Божинова"</t>
+          <t>ФтЕЦ "Кьосевци"</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Враца</t>
+          <t>Търговище</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Бяла Слатина</t>
+          <t>Антоново</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Бяла Слатина</t>
+          <t>Кьосевци</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>7702</t>
+          <t>41099</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.02975</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>23.05.2022</t>
+          <t>20.05.2021</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
@@ -1794,71 +1814,67 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>aa4dd7a0f112c4670500ba42ff0092d3b6dea964eb6c7c3bc1d95c8260f6bdbf</t>
+          <t>656c25c91579d8aee93d6379cad325a01bba7dc67d6b4484eb01d56bb370ca24</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Фантастико ЕООД</t>
+          <t>ТРИ ИНВЕСТ ЕООД</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>127624992</t>
+          <t>119656471</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Никола Козлево - Георги Сава Раковски"</t>
+          <t>ФтЕЦ "Ломци"</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Шумен</t>
+          <t>Търговище</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Никола Козлево</t>
+          <t>Попово</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Никола Козлево</t>
+          <t>Ломци</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>51651</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.02975</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>17.03.2023</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>30.01.2023</t>
-        </is>
-      </c>
+          <t>20.05.2021</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
@@ -1868,64 +1884,64 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>ef8a2c781b8f18085ca114bb3bb050e189e0d03338f504e4d046062f4d959ab4</t>
+          <t>2378aaa1b7a87b505de582be33850085905a369c665f160511fde253e9c05f57</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>БРАДЪРС КОМЕРС-2012 ООД</t>
+          <t>ТРИ ИНВЕСТ ЕООД</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>202307982</t>
+          <t>119656471</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Венеция"</t>
+          <t>ФтЕЦ "Манастирица"</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Плевен</t>
+          <t>Търговище</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Левски</t>
+          <t>Попово</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Малчика</t>
+          <t>Манастирица</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>46841</t>
+          <t>47007</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.199</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>13.10.2023</t>
+          <t>20.05.2021</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
@@ -1938,64 +1954,64 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>627e9ee7e9fda84dae9dcd5873b3a84aafa231dff1d0577725611c3ae2897026</t>
+          <t>f48c748104070ec3001bb1d61a55895fa41dd4ae8a52ee3ed4a1ab8ea12959ef</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Бул Инвест 25 ЕООД</t>
+          <t>АМИЧИ ООД</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>208627722</t>
+          <t>121000823</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Елит Газ Сливен - Церковски"</t>
+          <t>ФтЕЦ "Амичи"</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Бургас</t>
+          <t>Кюстендил</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Карнобат</t>
+          <t>Дупница</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Церковски</t>
+          <t>Дупница</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>78416</t>
+          <t>68789</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>07.09.2023</t>
+          <t>23.08.2026</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
@@ -2008,50 +2024,54 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>277eb47b7a05e482d0d62279dc06841e55eca7169a9ae636017d86abf347914a</t>
+          <t>568e1d52258498b9a9367702ee27cfb32fa8bd7c18a68d488519c91d93ebce96</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Марийка Крумова Георгиева</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
+          <t>САВ-РАЗГРАД ООД</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>200425074</t>
+        </is>
+      </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Георгиева-Каменово 1"</t>
+          <t>ФтЕЦ "Разград - Перистър"</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Сливен</t>
+          <t>Разград</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Нова Загора</t>
+          <t>Разград</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Каменово</t>
+          <t>Разград</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>35907</t>
+          <t>61710</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2061,7 +2081,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>01.12.2022</t>
+          <t>21.10.2021</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
@@ -2074,54 +2094,54 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>10073b02cedaf7be4f71dc135aed463ecc0b05b162a70dfb48e151f2d7219b66</t>
+          <t>dbbf2b06a9ef1a1c4eee227bb618cdb9d1d101473361493f8de5ca63d181799b</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ЕЛИТ ЕНЕРДЖИ 2025 ЕООД</t>
+          <t>БЕЛСИСТЕМС ООД</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>208627715</t>
+          <t>117522513</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Елит Газ - Сливен 5"</t>
+          <t>ФтЕЦ "Бяла-Русе-Хан Аспарух"-Закрит обект</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Сливен</t>
+          <t>Русе</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Сливен</t>
+          <t>Бяла</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Сливен</t>
+          <t>Бяла</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>67338</t>
+          <t>7603</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2131,7 +2151,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>18.01.2023</t>
+          <t>01.01.2022</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
@@ -2144,64 +2164,64 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>5972b0a7c49339a0c43cc7386c624d26b97791daeed0faf149c6bc92373cbd6c</t>
+          <t>d7bfd5d4668ed73e24862bc6946b33b62f6ec768423078574aeb6b9db64fe991</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Мирай Солар ЕООД</t>
+          <t>БОГИ - 6 ООД</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>207119475</t>
+          <t>102870243</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Малиново 5"</t>
+          <t>ФтЕЦ "Боги 6 - Бургас"</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Ловеч</t>
+          <t>Бургас</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ловеч</t>
+          <t>Бургас</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Малиново</t>
+          <t>Бургас</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>46396</t>
+          <t>7079</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>0.029975</t>
+          <t>0.108</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>22.03.2023</t>
+          <t>15.09.2022</t>
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
@@ -2214,60 +2234,64 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>66e9885eb33dc2f26962d1dad5b310087155ae36576884d0716ac561135ed7b1</t>
+          <t>94389017ef5eda6d419fa2aeef90430cf2f517a0a9777c3738b022fe4e5570a8</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>МАРИЯ ВАНЧЕВА СТАНЕВА</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
+          <t>ВОРТЕКС ВВ ЕООД</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>200857963</t>
+        </is>
+      </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Долни Пройновци"</t>
+          <t>ФтЕЦ "Вортекс ВВ - Априлово"</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Габрово</t>
+          <t>Стара Загора</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Габрово</t>
+          <t>Гълъбово</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Габрово</t>
+          <t>Априлово</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>14218</t>
+          <t>552</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>0.0297</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>02.03.2023</t>
+          <t>19.04.2022</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
@@ -2280,64 +2304,60 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>b82c1005989ab43f8067f1759763f8507bc7472afc30033b2dafc3e3e8b2c835</t>
+          <t>90a7becd14fec4412d5e85a5619b2addf343e5ec9745263d8c4dfc42a5a1c730</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Селекта ММ</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>204457404</t>
-        </is>
-      </c>
+          <t>Владимир Йорданов Манолов</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Селект ММ - Крепост"</t>
+          <t>ФтЕЦ "Силистра - Васил Левски"-Закрит обект</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Хасково</t>
+          <t>Силистра</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Димитровград</t>
+          <t>Силистра</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Крепост</t>
+          <t>Силистра</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>39668</t>
+          <t>66425</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>0.005</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>28.05.2024</t>
+          <t>16.08.2022</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
@@ -2350,34 +2370,34 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>922f727e0c7547a81db70c377ea4386ed0c32470873951a55fddd670a4712bd8</t>
+          <t>26de54eee02ee00a45fda5a904ddf48bcb3abbf63f41b67d67a4a7e85f446e1e</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>АНАБЕЛ-АННА БЕЛОВА ЕООД</t>
+          <t>РВК 1 ЕООД</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>203679327</t>
+          <t>200742345</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ФтЕЦ ''Анабел - Сливен 1"</t>
+          <t>ФтЕЦ "Калев Сух.чешма"</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2402,12 +2422,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>0.19855</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>22.04.2024</t>
+          <t>26.09.2022</t>
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
@@ -2420,64 +2440,64 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>cb5651104afac2e370f1d2dc30bdf98bb8f9207c5978ebc6288cf3045c9d7a96</t>
+          <t>2e16fbb8085312935f601762783b9904b7dc87c03bbd6105f6da2113d07fc761</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>АЛФА-ХИМ ЕООД</t>
+          <t>КОЗЛОДУЙ ООД</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>116559138</t>
+          <t>812212481</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Разград - Априлско въстание - 7"</t>
+          <t>ФтЕЦ "Козлодуй - Бургас"</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Разград</t>
+          <t>Бургас</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Разград</t>
+          <t>Бургас</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Разград</t>
+          <t>Бургас</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>61710</t>
+          <t>7079</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.199</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>06.08.2024</t>
+          <t>01.02.2023</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
@@ -2490,64 +2510,64 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>76386815d36ec75307d7da0808e31d6fd65e02f42b1a81ffecdba4fead87632f</t>
+          <t>a015802477f5a636decff777f01b94580ef3e343e564cd8de41980617547e7c1</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ФВЦ РИ ООД</t>
+          <t>ЗП ТОНЧО НИКОЛОВ ДРАГНЕВ</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>206748060</t>
+          <t>102907086</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ФтЕЦ "ФВЦ Ри - Гълъбово 1"</t>
+          <t>ФтЕЦ" Тончо Драгнев - Славянци 3"</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Стара Загора</t>
+          <t>Бургас</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Гълъбово</t>
+          <t>Сунгурларе</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Гълъбово</t>
+          <t>Славянци</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>18280</t>
+          <t>67115</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0.19712</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>07.08.2024</t>
+          <t>17.01.2023</t>
         </is>
       </c>
       <c r="J31" t="inlineStr"/>
@@ -2560,64 +2580,64 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>0e48564221f7aead14f2d6bc89e4b6eea754007bfd03154a0704f7e0c93289fd</t>
+          <t>9cf9ea0812f734e95cdff5b87c9c7c60b241026a7fb99e2e13c8ec4e0c92089d</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ЕВРОИНВЕСТ МАСЛИНКОВ ЕООД</t>
+          <t>Джи Ем Сън Систем Солар ЕООД</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>203018977</t>
+          <t>206684272</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Евроинвест Маслинков - Желю войвода 5"</t>
+          <t>ФтЕЦ "Алфатар - Димитър Талев"</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Сливен</t>
+          <t>Силистра</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Сливен</t>
+          <t>Алфатар</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Желю войвода</t>
+          <t>Алфатар</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>29194</t>
+          <t>415</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.1566</t>
+          <t>0.0396</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>21.03.2024</t>
+          <t>01.02.2023</t>
         </is>
       </c>
       <c r="J32" t="inlineStr"/>
@@ -2630,64 +2650,64 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>d819bf671a12f99ddd65becf45d7841baeaba590402765be1dc0f448bb1e6453</t>
+          <t>b2caa24cec7ea4c8890ce37dfe9d45dc1a95413f7976908068142fc0f5620099</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>БМД-МЕБЕЛИ ООД</t>
+          <t>ТРИТОН ЕНЕРДЖИ ЕООД</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>112091852</t>
+          <t>206147963</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ФтЕЦ "БМД Мебели - Пазарджик"</t>
+          <t>ФтЕЦ "Тритон 6"</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Пазарджик</t>
+          <t>Плевен</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Пазарджик</t>
+          <t>Гулянци</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Пазарджик</t>
+          <t>Милковица</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>55155</t>
+          <t>48204</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.138975</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>29.01.2024</t>
+          <t>27.03.2023</t>
         </is>
       </c>
       <c r="J33" t="inlineStr"/>
@@ -2700,54 +2720,54 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>7126650aec130a730da286e8187dff366f7d57e52995b5383ecb7f5ac995cb17</t>
+          <t>5405a91845462585663e6aba5be177c05f8d671d0227e75d9752e7282eea83ae</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>НИКИ ФРУТ ЕООД</t>
+          <t>ВАНИС 03 ООД</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>202763021</t>
+          <t>207074083</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Експрес мод"</t>
+          <t>ФтЕЦ "Ванис"</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Благоевград</t>
+          <t>Плевен</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Петрич</t>
+          <t>Долна Митрополия</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Кърналово</t>
+          <t>Тръстеник</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>40912</t>
+          <t>73359</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2757,7 +2777,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>04.08.2024</t>
+          <t>01.06.2023</t>
         </is>
       </c>
       <c r="J34" t="inlineStr"/>
@@ -2770,64 +2790,60 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>aa5571d5dc670d9ae091ae479161a591f699a52e295011a19b8ed2fdc376af36</t>
+          <t>5271887b092ec62d7f87bbb1cb53436e5bbee30846dfac9493a609ac57a05fa0</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ШИВАЧЕВО СОЛАР ЕООД</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>206858431</t>
-        </is>
-      </c>
+          <t>Ирена Жоресова Хаджиева</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Шивачево солар - Шивачево"</t>
+          <t>ФтЕЦ "Градище - Габрово - 1"</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Сливен</t>
+          <t>Габрово</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Твърдица</t>
+          <t>Севлиево</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Шивачево</t>
+          <t>Градище</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>15944</t>
+          <t>17542</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1.09935</t>
+          <t>0.014715</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>27.06.2025</t>
+          <t>15.06.2023</t>
         </is>
       </c>
       <c r="J35" t="inlineStr"/>
@@ -2840,64 +2856,64 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>be2247f1583a6bae777d549b8a4cba7a09283741a4c23c332ae96fdf74a97426</t>
+          <t>d979194fb02fa4df11db4bb408669ef75ddf49e4475af9f008c52b749e9728f3</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>АйЕнУай Груп ЕООД</t>
+          <t>"СОЛАРСИМО" - ЕООД</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>205851996</t>
+          <t>201372030</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Крушето - Георги Измирлиев - 1"</t>
+          <t>ФтЕЦ "Тренев и Синове"</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Велико Търново</t>
+          <t>Благоевград</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Горна Оряховица</t>
+          <t>Сандански</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Крушето</t>
+          <t>Склаве</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>40172</t>
+          <t>66785</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.5661</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>10.06.2024</t>
+          <t>24.04.2024</t>
         </is>
       </c>
       <c r="J36" t="inlineStr"/>
@@ -2910,67 +2926,71 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>8497603989efb6a90dbbaf54eca057252d74dd3a1c655e9d10b0f7037e96aabf</t>
+          <t>b449472e2e2d9fbbc6d3efa3741711f1861de4727ed7799b52e8b13c6eb47619</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ЕПОЗИД БГ ВАРНА ЕООД</t>
+          <t>Селекта ММ</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>202442916</t>
+          <t>204457404</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Провадия - 3"</t>
+          <t>ФтЕЦ "Селект ММ - Крепост"</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Варна</t>
+          <t>Хасково</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Провадия</t>
+          <t>Димитровград</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Провадия</t>
+          <t>Крепост</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>58503</t>
+          <t>39668</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0.79755</t>
+          <t>2.37115</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>28.07.2025</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr"/>
+          <t>20.03.2026</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>28.05.2024</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
@@ -2980,64 +3000,64 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>9797b6e97ac96564876b6bff58ec00375c8f27c940402396f275817556427359</t>
+          <t>53d53122a13cf472bcdd4a8ed3d93ab689f2358993b0392cf1d74cedd190569a</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>СОФИМИРА ЕООД</t>
+          <t>АЛУМИНА ЕЛИТ 2003 ЕООД</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>204917404</t>
+          <t>104612589</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Софимира"</t>
+          <t>ФтЕЦ "Велико Търново - Дълга Лъка - 2"</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>София-Област</t>
+          <t>Велико Търново</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Драгоман</t>
+          <t>Велико Търново</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Драгоман</t>
+          <t>Велико Търново</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>23409</t>
+          <t>10447</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>08.10.2025</t>
+          <t>16.05.2024</t>
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
@@ -3050,60 +3070,64 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>b4ab87ef6cbda05cfc7fcf3871d26ab4bbaabe028286abd3a4242ba5be9f8cde</t>
+          <t>915f50162cbfcaa7c6ea351c1dcb9ba9eb94a396380fea6affd5c5e763a547ca</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Искра Маринова Пантелеева</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
+          <t>БРИТ ТРЕЙД ЕООД</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>206825851</t>
+        </is>
+      </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Свищов - Райчо Николов"</t>
+          <t>ФтЕЦ "Брит Трейд - Граф Игнатиево 1"</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Велико Търново</t>
+          <t>Пловдив</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Свищов</t>
+          <t>Марица</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Свищов</t>
+          <t>Граф Игнатиево</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>65766</t>
+          <t>17806</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>11.11.2024</t>
+          <t>02.10.2023</t>
         </is>
       </c>
       <c r="J39" t="inlineStr"/>
@@ -3116,64 +3140,64 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>0596d1dc4964bd5f4e5da3044df8c5c4b60f2a6e3297ff0efeeb901584353aa9</t>
+          <t>549a739694c90ad040ca024ec4efe186fb2029edf302dbf1b9c5b927796d7287</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>АВС - ИНЖЕНЕРИНГ - Н ООД</t>
+          <t>Елисей Тех ЕООД</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>128031110</t>
+          <t>204431982</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ФтЕЦ "АВС Инженеринг - Сливен 1"</t>
+          <t>ФтЕЦ "Елисей тех"</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Сливен</t>
+          <t>Плевен</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Сливен</t>
+          <t>Кнежа</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Сливен</t>
+          <t>Кнежа</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>67338</t>
+          <t>37376</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>07.10.2025</t>
+          <t>15.08.2024</t>
         </is>
       </c>
       <c r="J40" t="inlineStr"/>
@@ -3186,64 +3210,64 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>0840e4140b3336cad241101bb41f29f313b50f17c5203d551981d2fb20747884</t>
+          <t>b25abb7c17e6b20f51485c8f463672e492507c1b0b125435c016af88e1ecac98</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ПАГА ООД</t>
+          <t>КРИСТАЛ ГЛАС-ХОЛДИНГ АД</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>203608878</t>
+          <t>206062669</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Обретеник - Отец Паисий"</t>
+          <t>ФтЕЦ "Дивдядово - Велики Преслав - 2"</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Русе</t>
+          <t>Шумен</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Борово</t>
+          <t>Шумен</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Обретеник</t>
+          <t>Шумен</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>53117</t>
+          <t>83510</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.1991</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>19.11.2025</t>
+          <t>02.10.2024</t>
         </is>
       </c>
       <c r="J41" t="inlineStr"/>
@@ -3256,60 +3280,60 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>0813d983f920cc4422311892866ba998d8c289f77de52be300a2ddbd30b5f451</t>
+          <t>93791dbfec7445792cc88f62ab3ebb355f4aec3fcacf20f6fca2ad29c4a9fe1e</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Валентин Николаев Вълков</t>
+          <t>Борислав Любомиров Илиев</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Валентин Вълков"</t>
+          <t>ФтЕЦ "Борислав Илиев"</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Плевен</t>
+          <t>София-град</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Белене</t>
+          <t>Столична</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Белене</t>
+          <t>Нови Искър</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>3366</t>
+          <t>357</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.0297</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>12.09.2025</t>
+          <t>20.12.2023</t>
         </is>
       </c>
       <c r="J42" t="inlineStr"/>
@@ -3322,64 +3346,60 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>5d85385f8e51ce24d8d16e76e6f238f0a89ddcb12b0d364cfe46ea5a0fe68aad</t>
+          <t>d5b0a95b8a5ff210bbb65dae856b64801974a2f2ba86943a7568622496a8f95e</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ЕЛЕКТРООБЗАВЕЖДАНЕ КАЗАНЛЪК ЕООД</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>123727369</t>
-        </is>
-      </c>
+          <t>Стайко Тодоров Костадинов</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Електрообзавеждане - Тъжа"</t>
+          <t>ФтЕЦ "Пенка Костадинова - Камено"</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Стара Загора</t>
+          <t>Бургас</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Павел баня</t>
+          <t>Камено</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Тъжа</t>
+          <t>Камено</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>73540</t>
+          <t>35883</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>0.07744</t>
+          <t>0.1188</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>27.08.2025</t>
+          <t>16.08.2024</t>
         </is>
       </c>
       <c r="J43" t="inlineStr"/>
@@ -3392,64 +3412,60 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>0b17f15622eca1dda25112d7c28aaa0404cd3a80df7dbeae0cf7b7e1724d853f</t>
+          <t>c785809a26118c7e8c98695d1adeba203c77dfbcd22617872dfd610fc17e6a9c</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ФЕЦ ГУРКОВО ООД</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>207309745</t>
-        </is>
-      </c>
+          <t>Бисерка Георгиева Атанасова</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ФтЕЦ Гурково - Гурково</t>
+          <t>ФтЕЦ "Альоша Атанасов"</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Стара Загора</t>
+          <t>Плевен</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Гурково</t>
+          <t>Левски</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Гурково</t>
+          <t>Обнова</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>18157</t>
+          <t>53089</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0.49808</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>17.09.2025</t>
+          <t>24.07.2023</t>
         </is>
       </c>
       <c r="J44" t="inlineStr"/>
@@ -3462,64 +3478,64 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>0345ac6cdae3763d9b96ee5abc1f9f8fc59297838828f2409baca7521dd49354</t>
+          <t>47d3a7a8b1e80861bc065e0aa7309757e92a9440c8962e4244f6d4618a473f3f</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ЕКО ВОЛТ ООД</t>
+          <t>Живот в радост ЕООД</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>208629164</t>
+          <t>207094851</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Солар парк Разделна - Разделна 1"</t>
+          <t>ФтЕЦ ,,Живот в радост - Русокастро''</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Стара Загора</t>
+          <t>Бургас</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Гълъбово</t>
+          <t>Бургас</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Разделна</t>
+          <t>Бургас</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>61755</t>
+          <t>7079</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.029975</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>15.04.2026</t>
+          <t>27.02.2024</t>
         </is>
       </c>
       <c r="J45" t="inlineStr"/>
@@ -3532,64 +3548,60 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>5653f1e4b9df0b85ff6a0c451f48ebbf5dae20a92f0567ba93872a020f7a9900</t>
+          <t>767abcefe6343887809d6f260825b968b08e729d38f1c3d0ff68893fa7f81e81</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ХЛЯБ И ХЛЕБНИ ИЗДЕЛИЯ ЕООД</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>128567573</t>
-        </is>
-      </c>
+          <t>Стоянка Петрова Спирова</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Новосолар - Хлябово"</t>
+          <t>ФтЕЦ "Стоянка Спирова - Оризари"</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Хасково</t>
+          <t>Пловдив</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Тополовград</t>
+          <t>Родопи</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Хлябово</t>
+          <t>Оризари</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>77325</t>
+          <t>53833</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>0.149175</t>
+          <t>0.0276</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>18.02.2026</t>
+          <t>01.02.2024</t>
         </is>
       </c>
       <c r="J46" t="inlineStr"/>
@@ -3602,64 +3614,64 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>59db71d7736d664b75cc26b425c92a19f1a82b6d66a322d5d34a99c774a96b18</t>
+          <t>a050f8c67d6098f52f504dd85eb69ffb3d6e6bbd9048aca2f6f647273b412a3d</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ХЛЯБ И ХЛЕБНИ ИЗДЕЛИЯ ЕООД</t>
+          <t>"БИО ТРЕЕ" ЕООД</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>128567573</t>
+          <t>203774259</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ФТЕЦ "Новосолар - Хлябово 2"</t>
+          <t>ФтЕЦ "Комарево"</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Хасково</t>
+          <t>Варна</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Тополовград</t>
+          <t>Провадия</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Хлябово</t>
+          <t>Комарево</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>77325</t>
+          <t>38114</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>0.119775</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>18.02.2026</t>
+          <t>30.01.2024</t>
         </is>
       </c>
       <c r="J47" t="inlineStr"/>
@@ -3672,64 +3684,64 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>4d2628658aa1881c066e4bb72616dcde54eb366e6f1ae4d58211d6d2cce54a16</t>
+          <t>c9d6b5fc280d23d47631a6a5570ccad31a7eceb66d6c4ec7876f87255c200bca</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Сюприйм естейтс ООД</t>
+          <t>"БИО ТРЕЕ" ЕООД</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>206594323</t>
+          <t>203774259</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Сюприйм естейтс - Меричлери 1"</t>
+          <t>ФтЕЦ "Тутраканци - 5"</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Хасково</t>
+          <t>Варна</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Димитровград</t>
+          <t>Провадия</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Меричлери</t>
+          <t>Тутраканци</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>47843</t>
+          <t>73506</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>0.02958</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>20.06.2025</t>
+          <t>13.03.2024</t>
         </is>
       </c>
       <c r="J48" t="inlineStr"/>
@@ -3742,64 +3754,64 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>33056db6ce0bf462131442531ec47b5bcb9d95fd9bd763c5f3b087307239fe05</t>
+          <t>41a6c50bdd90ecf2273aa60cd76853c87ead3b2f78ccbd253d28c935dd874651</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ЗОНА СЛЪНЦЕ ООД</t>
+          <t>ЗП ТОНЧО НИКОЛОВ ДРАГНЕВ</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>208038026</t>
+          <t>102907086</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Начков - Зайчари 1"</t>
+          <t>ФтЕЦ "Тончо Драгнев - Славянци 4"</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Сливен</t>
+          <t>Бургас</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Сливен</t>
+          <t>Сунгурларе</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Зайчари</t>
+          <t>Славянци</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>30257</t>
+          <t>67115</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>0.18908</t>
+          <t>0.19866</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>20.03.2026</t>
+          <t>16.04.2024</t>
         </is>
       </c>
       <c r="J49" t="inlineStr"/>
@@ -3812,64 +3824,64 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>837079579c901688b7810241bdef957fd0d42c19657ffc52704d9026fe6b59f1</t>
+          <t>113c531f3752b20639ac2b1cc8ba50d8dc7fd1dfe2d2104593d3d307a0bac256</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>БРИТ ТРЕЙД ЕООД</t>
+          <t>Фонд Зелена Енергия ООД</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>206825851</t>
+          <t>208722729</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Брит Трейд Граф Игнатиево 8"</t>
+          <t>ФтЕЦ "Нетикс Енерджи - Малък Дол 4"</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Пловдив</t>
+          <t>Стара Загора</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Марица</t>
+          <t>Братя Даскалови</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Граф Игнатиево</t>
+          <t>Малък дол</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>17806</t>
+          <t>49998</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>0.14112</t>
+          <t>0.1703</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>11.05.2026</t>
+          <t>18.07.2024</t>
         </is>
       </c>
       <c r="J50" t="inlineStr"/>
@@ -3882,64 +3894,64 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>2802da878034fa695215454de4c69600485fe93267120fe97955978da61b9823</t>
+          <t>a74eec67d86bdf34cf59c5f7382f88f1f2447f05c5ed9799d81bfed5ba46c70a</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ПВ ПЛАНТС ЕООД</t>
+          <t>АПОЛОНИЯ РИЗОРТ ООД</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>207334563</t>
+          <t>200180098</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ФтЕЦ "ПВ Плантс"</t>
+          <t>ФтЕЦ "Аполония ризорт - Черноморец"</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>София-Област</t>
+          <t>Бургас</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Ихтиман</t>
+          <t>Созопол</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Веринско</t>
+          <t>Черноморец</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>10690</t>
+          <t>81178</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>19.12.2025</t>
+          <t>11.12.2024</t>
         </is>
       </c>
       <c r="J51" t="inlineStr"/>
@@ -3952,64 +3964,64 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>8eea1ef0b84cb5a3265f245ec1779d270a618b7be039de61dd080407a786865a</t>
+          <t>2551abcebff1aba6d5649444cbd21c9ffd412770c91c494dca29b1190a12cfa9</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ГРИФИТ ПЕТРОЛ ЕООД</t>
+          <t>ЕВРОПЕТРОЛ ЕООД</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>202668662</t>
+          <t>102636724</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Грифит Петрол - Сливен 2"</t>
+          <t>ФтЕЦ "Европетрол - Бургас 2"</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Сливен</t>
+          <t>Бургас</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Сливен</t>
+          <t>Бургас</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Сливен</t>
+          <t>Бургас</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>67338</t>
+          <t>7079</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>0.029975</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>20.08.2025</t>
+          <t>11.08.2026</t>
         </is>
       </c>
       <c r="J52" t="inlineStr"/>
@@ -4022,34 +4034,34 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>405c1a4d1ab49349d6c8faaf46eefdee43d3e08b8d5b1c996e1d9bd563997283</t>
+          <t>0b430da868a33bf5285b71c58ff4b50a7a0588615a215de9e0c0d23b375958be</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Новосолар ООД</t>
+          <t>ЕВРОПЕТРОЛ ЕООД</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>207487096</t>
+          <t>102636724</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Новосолар - Садово 2"</t>
+          <t>ФтЕЦ "Европетрол - Бургас 1"</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4059,27 +4071,27 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Сунгурларе</t>
+          <t>Бургас</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Садово</t>
+          <t>Бургас</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>65111</t>
+          <t>7079</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>0.1983</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>07.05.2026</t>
+          <t>11.08.2026</t>
         </is>
       </c>
       <c r="J53" t="inlineStr"/>
@@ -4092,64 +4104,64 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>1724e2349b8d6dd31388d4189660e497fb5494c3b8b863bd007c1fa903a54284</t>
+          <t>f22fd83b4e1e17e610e6d7aab2eeea6888e2aabfda6b272dbd786ef15e108df0</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Новосолар ООД</t>
+          <t>ЕНДЮРАНС ИНВЕСТМЪНТС ЕАД</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>207487096</t>
+          <t>208636415</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Новосолар - Садово 1"</t>
+          <t>ФтЕЦ "Алфасист складова база"</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Бургас</t>
+          <t>Монтана</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Сунгурларе</t>
+          <t>Монтана</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Садово</t>
+          <t>Монтана</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>65111</t>
+          <t>48489</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>0.12987</t>
+          <t>0.193855</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>07.05.2026</t>
+          <t>18.06.2025</t>
         </is>
       </c>
       <c r="J54" t="inlineStr"/>
@@ -4162,60 +4174,64 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>12fe4abf1009c54e4908eb4d0053c4bd449ad6e40b8906300c952785a957b92f</t>
+          <t>4cd843bc72e83fa1708a97bb46c67e988280c598651720f7b00728c3263789ef</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Валентин Николаев Вълков</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr"/>
+          <t>ТОМИ СИСТЪРС ООД</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>206934509</t>
+        </is>
+      </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Валентин Вълков 2"</t>
+          <t>ФтЕЦ "Тетово - Елин Пелин"</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Плевен</t>
+          <t>Русе</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Белене</t>
+          <t>Русе</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Белене</t>
+          <t>Тетово</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>3366</t>
+          <t>72357</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.0297</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>01.01.2026</t>
+          <t>17.01.2025</t>
         </is>
       </c>
       <c r="J55" t="inlineStr"/>
@@ -4228,64 +4244,64 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>7edf7eaae817ce0d9bad1cba37b2c5d38c66b5354b8b06c752f193bbd8a206e0</t>
+          <t>6e29bef085819356c3572fb54313de3a82c1c844de26cc7a16138e31fc2cd16c</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ПЛАМЕН ПЕТРОВ - 2010 ЕООД</t>
+          <t>БЕЛЛ ИНВЕСТМЪНТ ЕООД</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>201124526</t>
+          <t>205847108</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Пламен Петров - Събрано"</t>
+          <t>ФтЕЦ "Белл Инвестмънт - Асеновград 2"</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Сливен</t>
+          <t>Пловдив</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Нова Загора</t>
+          <t>Куклен</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Събрано</t>
+          <t>Куклен</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>70456</t>
+          <t>40467</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>0.08964</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>21.11.2025</t>
+          <t>31.07.2025</t>
         </is>
       </c>
       <c r="J56" t="inlineStr"/>
@@ -4298,34 +4314,34 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>24278e4b1b5ea29053674f22a7edbf920eb070d010510a2a5fb0c9f7406259bc</t>
+          <t>63e8a234546e1a36e6ba4d40261d2f507f328f79612298ef61788b0b4ba71231</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>АИП СОЛАР ООД</t>
+          <t>ЕНЕРДЖИ 83 ЕООД</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>207300810</t>
+          <t>206017147</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ФтЕЦ "АИП Солар - Събрано"</t>
+          <t>ФтЕЦ "Енерджи 83 - Гергевец 2"</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -4335,27 +4351,27 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Нова Загора</t>
+          <t>Сливен</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Събрано</t>
+          <t>Гергевец</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>70456</t>
+          <t>14800</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>0.14991</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>06.02.2026</t>
+          <t>16.05.2024</t>
         </is>
       </c>
       <c r="J57" t="inlineStr"/>
@@ -4368,64 +4384,64 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>e19f79c8665844a16fb57ae57c6d1738ef5056bdc9c1b742b38b52f12447cf70</t>
+          <t>c51079e920e9321a1e442eb707de9266de0a4bd0d3aaafd429b1f213e4156e5b</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>СПИРОВ ООД</t>
+          <t>ХЕЛЕКТ АД</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>119673990</t>
+          <t>202358674</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Спиров - Сливен 1"</t>
+          <t>ФтЕЦ "ПВ Алианц - Генерал Тошево"</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Сливен</t>
+          <t>Ямбол</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Сливен</t>
+          <t>Тунджа</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Сливен</t>
+          <t>Генерал Тошево</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>67338</t>
+          <t>14725</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>0.19765</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>02.03.2026</t>
+          <t>01.07.2025</t>
         </is>
       </c>
       <c r="J58" t="inlineStr"/>
@@ -4438,64 +4454,60 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>ba7a2a46e340df47507e2b1b553b9786057f405a7609bae5a4f9758f318945f5</t>
+          <t>e1a5701a725f6aad1f41a0a3ed812294a74f3da4d9c515f93358acb8003612cf</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ДИМОВ ГРУП БГ ООД</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>204398475</t>
-        </is>
-      </c>
+          <t>Ганка Тодорова Руджелева</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Димов Груп - Каблешково 1"</t>
+          <t>ФтЕЦ Дряновец-Разград-Гоце Делчев</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Бургас</t>
+          <t>Разград</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Поморие</t>
+          <t>Разград</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Каблешково</t>
+          <t>Дряновец</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>35033</t>
+          <t>23902</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>0.999</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>08.06.2026</t>
+          <t>31.03.2025</t>
         </is>
       </c>
       <c r="J59" t="inlineStr"/>
@@ -4508,64 +4520,60 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>7a147bf8112e2bd17ac11f8460d4ea26693a5ebb91a0f359d15a667ce410761c</t>
+          <t>ca7e8994d38b5dd69b790244563bfab94693a0048782c54b52eceb39409c8fed</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>СОЛАР СЕРВИЗ КОНСУЛТ ЕООД</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>201817473</t>
-        </is>
-      </c>
+          <t>Стайко Тодоров Костадинов</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Солар СК - Лозен 2"</t>
+          <t>ФтЕЦ "Стайко Костадинов - Камено"</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Хасково</t>
+          <t>Бургас</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Любимец</t>
+          <t>Камено</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Лозен</t>
+          <t>Камено</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>44077</t>
+          <t>35883</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>0.07973</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>22.05.2026</t>
+          <t>01.09.2025</t>
         </is>
       </c>
       <c r="J60" t="inlineStr"/>
@@ -4578,64 +4586,64 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>53b2627c1ad69ee8a9a55723dd9fa5fbe8d4ee8592f1513151f70b184497cdf7</t>
+          <t>ab49c182cab638c5ac8363555c80c41ac7d75d70a2b0fe76d4da30303b4f72f9</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ДМТ 2006 ЕООД</t>
+          <t>ЕТ ШАНС-МИЛКО БАЙЧЕВ</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>123755728</t>
+          <t>104040064</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ФтЕЦ "ДМТ- Кирилово 3"</t>
+          <t>ФтЕЦ "Поликраище - Ивайло - 1"</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Стара Загора</t>
+          <t>Велико Търново</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Стара Загора</t>
+          <t>Горна Оряховица</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Кирилово</t>
+          <t>Поликраище</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>36899</t>
+          <t>57217</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>0.3135</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>04.06.2026</t>
+          <t>12.09.2025</t>
         </is>
       </c>
       <c r="J61" t="inlineStr"/>
@@ -4648,67 +4656,71 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>9c7c5d943d30a92b757640fbdfaea5c516e600b235d07cb7b3f11febe39893dd</t>
+          <t>fbc6a05909658977aaad460283c6bcd217fa8a50ef5cb366c2d24392e3aa9a72</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Ем Пи Пи Ви ЕООД</t>
+          <t>ТЕНЕВО СОЛАР ТЕХНОЛОДЖИС ЕАД</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>200746742</t>
+          <t>206511621</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Ем Пи Пи Ви - Тополовград 2"</t>
+          <t>ФтЕЦ "Тенево Солар"</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Хасково</t>
+          <t>Ямбол</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Тополовград</t>
+          <t>Тунджа</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Тополовград</t>
+          <t>Тенево</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>72761</t>
+          <t>72240</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>228.1</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>08.06.2026</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr"/>
+          <t>21.05.2026</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>11.06.2025</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
@@ -4718,64 +4730,64 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>6ced4d8abca0642e9aab41d06d62db57286fcb5875b73d89ca7272f1ec723276</t>
+          <t>5112c5e02be5e596a8aa449da864564c6de7cf9541a801e8a13a7c192d0ca3aa</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ДОН АНГУС ЕООД</t>
+          <t>ЮИДП ДП ТП ДЛС НЕСЕБЪР</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>204699667</t>
+          <t>2016176540172</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Хлябово - Доньо Костов Стайков"</t>
+          <t>ФтЕЦ "ТП Държавно ловно стопанство - Несебър"</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Хасково</t>
+          <t>Бургас</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Тополовград</t>
+          <t>Несебър</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Хлябово</t>
+          <t>Несебър</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>77325</t>
+          <t>51500</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.0297</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>27.05.2026</t>
+          <t>25.09.2025</t>
         </is>
       </c>
       <c r="J63" t="inlineStr"/>
@@ -4788,64 +4800,64 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>bdbf40768ee63bde582586949b3bf5bf85b70b74684214db3f391e1773f10751</t>
+          <t>e2503d43f95f957800777cf5db6b3d093ec5723ed0383c2d02a8f12a2dba68d6</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>АЛФА СОЛАР -Д ООД</t>
+          <t>ИМПЕКС 2004 ЕООД</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>207421146</t>
+          <t>206539476</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Шумен - под село"</t>
+          <t>ФтЕЦ "Импекс - Сливен 2"</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Шумен</t>
+          <t>Сливен</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Шумен</t>
+          <t>Сливен</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Шумен</t>
+          <t>Сливен</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>83510</t>
+          <t>67338</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>0.4686</t>
+          <t>0.199</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>19.06.2026</t>
+          <t>12.11.2025</t>
         </is>
       </c>
       <c r="J64" t="inlineStr"/>
@@ -4858,64 +4870,60 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>c3e1230317d1d6062e7db6ac99058fd888878745aee749dae19fed73d5a36fb6</t>
+          <t>c3bf6f0366075934a8df5e36a640f26e45cca90e893feae55d863467e221581e</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ВД ЕКО ЕНЕРГОПРОЕКТ ЕООД</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>206796192</t>
-        </is>
-      </c>
+          <t>Камен Димитров Шишков</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ФтЕЦ "ВД Енергопроект - Оряховец"</t>
+          <t>ФтЕЦ "Павел - 1"</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Смолян</t>
+          <t>Велико Търново</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Баните</t>
+          <t>Полски Тръмбеш</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Оряховец</t>
+          <t>Павел</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>54002</t>
+          <t>55018</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>0.20001</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>07.04.2026</t>
+          <t>24.10.2025</t>
         </is>
       </c>
       <c r="J65" t="inlineStr"/>
@@ -4928,64 +4936,64 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>0b003eba5a21921714766e69b9463c4edd2e95a4e626ba4276d2b5f013fbf1cf</t>
+          <t>8d3b6b18a0d4f7cb6e70a229da7f150742fcbdd9289c0ef5d0b27a495c7e9a94</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>СТРОЙ ГРУП ИЛИЕВИ ЕООД</t>
+          <t>ЕС ПИ ЕНЕРДЖИ ЕНД УОТЪР ООД</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>119679139</t>
+          <t>207180791</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Строй груп - Сливен 2"</t>
+          <t>ФтЕЦ "Ес Пи Енерджи Енд Уотър - Неделево"</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Сливен</t>
+          <t>Пловдив</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Сливен</t>
+          <t>Съединение</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Сливен</t>
+          <t>Неделево</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>67338</t>
+          <t>51305</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>0.02915</t>
+          <t>0.029945</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>23.03.2026</t>
+          <t>22.07.2025</t>
         </is>
       </c>
       <c r="J66" t="inlineStr"/>
@@ -4998,64 +5006,64 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>4b3dee7553f0d8363a3bdc26206292468ce2d754a19eb84660ffef8b99405a82</t>
+          <t>30fd97c228589b95a9912e5d3490ebd90ce3afc00336989ba9a01f494b6bad0b</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>СОЛАР ГРУП ОКИ ЕООД</t>
+          <t>ТЕХНОКА СЕРВИЗ ЕООД</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>206957803</t>
+          <t>201737041</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Окан 3"</t>
+          <t>ФтЕЦ "ГИД Пауър -Жребино</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Плевен</t>
+          <t>Ямбол</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Никопол</t>
+          <t>Елхово</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Никопол</t>
+          <t>Жребино</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>51723</t>
+          <t>29516</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.09976</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>01.08.2025</t>
+          <t>01.03.2026</t>
         </is>
       </c>
       <c r="J67" t="inlineStr"/>
@@ -5068,60 +5076,64 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>ba537031e6af14e5f4da7341dbae92ee8b3943e0d381a0630f490501e209b1f9</t>
+          <t>3624a0bb40522c5ca41ed99bc5d4e7be9af2c996ca56151d09603ca7c881b870</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ДАНИЕЛА ЛИЧКОВА ИВАНОВА</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr"/>
+          <t>ХИДРО СИСТЕМИ МАРИЦА ЕООД</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>205891211</t>
+        </is>
+      </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ФтЕЦ ,,Даниела Иванова Белотинци 2"</t>
+          <t>ФтЕЦ "ММ Смарт Енерджи - Първомай"</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Монтана</t>
+          <t>Пловдив</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Монтана</t>
+          <t>Първомай</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Белотинци</t>
+          <t>Първомай</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>3722</t>
+          <t>59080</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>0.0295</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>16.02.2026</t>
+          <t>17.09.2025</t>
         </is>
       </c>
       <c r="J68" t="inlineStr"/>
@@ -5134,64 +5146,64 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>ba6f050fec9a719f1acb25832fe07710f79f5d73638dcdbec4f334a9d3c080e4</t>
+          <t>fa5f8869fe17b4957fb5bac392e24a45361e8b07a1b7ea92a27e3a97b15c8ac9</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ВИЗАВА ООД</t>
+          <t>"ГеоСоларити" ЕООД</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>119604909</t>
+          <t>206682271</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Визава - Голям извор"</t>
+          <t>ФтЕЦ "Тутракан - 3"</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Хасково</t>
+          <t>Силистра</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Стамболово</t>
+          <t>Тутракан</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Голям извор</t>
+          <t>Тутракан</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>15775</t>
+          <t>73496</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>0.11985</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>02.06.2026</t>
+          <t>16.12.2025</t>
         </is>
       </c>
       <c r="J69" t="inlineStr"/>
@@ -5204,64 +5216,64 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>2ad84e737378bffe306d2f5367ae7f1ef3ab4e94f1057304376e07cbf4d465fa</t>
+          <t>f89dd98cd457fc609d21fd961664f20f956d39fe5b8f4483711f996cfab9dc93</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Исо Трейд ЕООД</t>
+          <t>ТОДОР ДАМЯНОВ - МД ООД</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>206762963</t>
+          <t>104536480</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Исо трейд 6"</t>
+          <t>ФтЕЦ "Велико Търново - Стоян Коледаров"</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Враца</t>
+          <t>Велико Търново</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Мизия</t>
+          <t>Велико Търново</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Мизия</t>
+          <t>Велико Търново</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>48043</t>
+          <t>10447</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>1.598</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>14.04.2026</t>
+          <t>12.09.2024</t>
         </is>
       </c>
       <c r="J70" t="inlineStr"/>
@@ -5274,17 +5286,2455 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>c43ec527630db6aef76af7345c7d0e48fe30e7616174a1993e7c19bb86661cb7</t>
+          <t>2bab61a0e424beb6edabaef84783e22390eea7b6f3a3f40cb881976a1f2624b0</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>2026-08-01T10:10:33+03:00</t>
+          <t>2026-09-01T09:45:04+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>ТОДОР ДАМЯНОВ - МД ООД</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>104536480</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>ФтЕЦ "Лясковец - Оборище - 6"</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Велико Търново</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Лясковец</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Лясковец</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>44793</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>05.03.2026</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>Слънчева енергия</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>ab7bdfd85a1a3ecb32bf9c00dd45ebdf2e60a16d363dcc79b87efd50e817f4ec</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:45:04+03:00</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:45:04+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>БОЙЧО ОГНЯНОВ 1 ООД</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>113549797</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>ФтЕЦ "Уоу маркет"</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Перник</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Радомир</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Радомир</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>61577</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>0.19</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>24.06.2026</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>Слънчева енергия</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>b7f72136ecc9a449e96321a29175435992501d4e8ef61d5938edfc896137d9af</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:45:04+03:00</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:45:04+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>ЕЕ ИНВЕСТ ВЪЛЧИ ДОЛ ЕООД</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>206949009</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>ФтЕЦ "Вълчи дол - 4"</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Варна</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Вълчи дол</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Вълчи дол</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>12574</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>10.06.2026</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>Слънчева енергия</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>97f1269b2072830e2f27fd30b0d9e7c7543718c2d9359e2ed4d85e9536265a5a</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:45:04+03:00</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:45:04+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>ИНКОМС-ИНСТРУМЕНТИ И МЕХАНИКА АД</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>121110956</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>ФтЕЦ Инкомс инструменти и механика</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>София-град</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Столична</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>София</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>68134</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>20.05.2026</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Слънчева енергия</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>6f18274456bbedb63ca8fa3ca610bf66d43bfe14f81b5cc8d34283685fd5e546</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:45:04+03:00</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:45:04+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Солар Еко КД ООД</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>206715312</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>ФтЕЦ "Суворово - 2"</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Варна</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Суворово</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Суворово</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>70175</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>0.15865</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>16.06.2026</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>Слънчева енергия</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>92764fc97a8e66004cffa7a3f5b487d21567b1b764c5413d0eba52c8f8010dcd</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:45:04+03:00</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:45:04+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Екатерина Дянкова Андреева</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>ФтЕЦ "Екатерина Андреева - Раклица 1"</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Бургас</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Карнобат</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Раклица</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>62027</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>0.06042</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>29.05.2026</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>Слънчева енергия</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>9984aac76f5bf69fadc7346485202585853ca5ec7ad7ca595467897befe6ad3c</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:45:04+03:00</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:45:04+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Кооперация ЗК БАТА</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>812176576</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>ФтЕЦ "ЗК Бата - Бата"</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Бургас</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Поморие</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Бата</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>2810</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>0.1988</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>10.10.2024</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>Слънчева енергия</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>8550ea3add80eb2ae6a3d3c35ecc3cfb5d9ac68afd129e4be6970c73a34e01a8</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:45:04+03:00</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:45:04+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>М.К.Р. ЕООД</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>128621055</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>ФтЕЦ "Ямбол - М.К.Р."</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Ямбол</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Ямбол</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Ямбол</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>87374</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>0.0297</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>13.09.2025</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>Слънчева енергия</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>2c052790afae4e8bf4b4530fdb67755e92076dac2f9550b592b59866804bf7ba</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:45:04+03:00</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:45:04+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>ГАРАНТ - Б ЕООД</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>119616950</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>ФтЕЦ "Гарант Б - Сливен 1"</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Сливен</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Сливен</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Сливен</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>67338</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>0.089835</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>13.03.2026</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>Слънчева енергия</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>906f6778f37ebd0862ac416d7821b660d066c5be4d8f33912ae7fa64c7467945</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:45:04+03:00</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:45:04+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>ЕВАЛДИ ЕООД</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>204890996</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>ФтЕЦ "Евалди - Руманя"</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Стара Загора</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Стара Загора</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Руманя</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>63301</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>18.05.2026</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>Слънчева енергия</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>a4b8a8caa15917b24a977a909a92d59d971938d5e3f5d66bfeb656a11065b479</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:45:04+03:00</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:45:04+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>ПВ АЛИАНЦ ООД</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>205373286</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>ФтЕЦ "ПВ Алианц - Държава 4"</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Стара Загора</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Чирпан</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Държава</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>24623</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>0.09975</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>04.06.2026</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>Слънчева енергия</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>90272c918ba7d1fefb6d671b476665e3a5c71cffa448b51dced0766e22502693</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:45:04+03:00</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:45:04+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>СОЛАР ЦЕНТЪР ГРУП ЕООД</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>208666853</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>ФтЕЦ "Тракер Венци"</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Перник</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Брезник</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Конска</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>41126</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>07.10.2025</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>Слънчева енергия</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>ec2226165e1dd9c2e687e251ab21570cd45beca73e1ac0a9dc4baa23cf4c2b07</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:45:04+03:00</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:45:04+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Даниел Георгиев Петков</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>ФтЕЦ Даниел Петков -Шивачево</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Сливен</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Твърдица</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Шивачево</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>15944</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>0.0297</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>28.07.2026</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>Слънчева енергия</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>8f4c34e7c8a8f4b7933dd46dd4cab1dbe643862e511d907bd8b97e8e538a0169</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:45:04+03:00</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:45:04+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Волток Мега ООД</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>204882825</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>ФтЕЦ "Бяла - Русе - Чавдар войвода"</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Русе</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Бяла</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Бяла</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>7603</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>15.06.2026</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>Слънчева енергия</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>9c77558e1c928a78cf7ffb7aa88384a850c6f4eb966a406bc6eba8b948dfa452</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:45:04+03:00</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:45:04+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Карлово Солар Парк 2022 ЕООД</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>206796638</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>ФтЕЦ "Ведраре Солар"</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Пловдив</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Карлово</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Ведраре</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>10291</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>87.877</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>10.06.2026</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>Слънчева енергия</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>7ad1b9e48a8387560888067d0764cb320d75b9ac3a2433000a23ec20ac3e6f05</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:45:04+03:00</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:45:04+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Диамант 2023 ЕООД</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>207215712</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>ФтЕЦ "Диамант 2023"</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Враца</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Мездра</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Мездра</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>47714</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>21.10.2025</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>Слънчева енергия</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>2da1e50adbbd03791d9e6ca76130c2cd20b33aacbec6ceb89ecaff8109d2fa01</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:45:04+03:00</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:45:04+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>ДЕЯН ВАН КОВ ЕООД</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>200000178</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>ФтЕЦ "Капитановци 2"</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Видин</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Видин</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Капитановци</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>36141</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>0.09974</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>17.07.2026</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>Слънчева енергия</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>2726b548f37f2de31d98c8cf8eb49323579bc169c84bf4b13f3b80ae44a8c66d</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:45:04+03:00</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:45:04+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>СИСТЕМЕН АНАЛИЗ ООД</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>130992599</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>ФтЕЦ "Системен Анализ - Житница 2"</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Пловдив</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Калояново</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Житница</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>29475</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>01.07.2026</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>Слънчева енергия</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>4b02c1b2dba0d73d25d71893bb08101bcb7be4a0c8f42e35889f3ea2d951c557</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:45:04+03:00</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:45:04+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>ДЖОДИ ЕНЕРДЖИ ЕООД</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>205879629</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>ФтЕЦ "Джоди Енерджи - Синапово"</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Хасково</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Тополовград</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Синапово</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>66487</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>0.1298</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>16.07.2026</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>Слънчева енергия</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>7a4f01f831280118730fbd9e2a8d44c37234157f8b31daac966c7cdb8a8d7cbb</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:45:04+03:00</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:45:04+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>ГАЛАКСИ ИНТЕРНЕШЪНЪЛ ООД</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>200590688</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>ФтЕЦ "Галакси Интернешънъл - Васил Левски"</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Пловдив</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Карлово</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Васил Левски</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>10207</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>0.18768</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>15.07.2026</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>Слънчева енергия</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>b0dc2ef8836643a05075581bb0f28dbba07cf2ed834747e844f1d78f13ef5025</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:45:04+03:00</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:45:04+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>„ХОРИЗОНТ – ИВАНОВ” ЕООД</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>824121242</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>ФтЕЦ" Хоризонт Иванов "</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Плевен</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Плевен</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Плевен</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>56722</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>0.0597</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>10.08.2026</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>Слънчева енергия</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>448715520387ea5962b32f6c4facc8214f7c898083f93845ec7894fd938a305f</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:45:04+03:00</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:45:04+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>РОКИ - 80 ЕООД</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>206188017</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>ФтЕЦ "Роки 4"</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Плевен</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Долна Митрополия</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Тръстеник</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>73359</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>26.06.2026</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>Слънчева енергия</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>2329ba378d5870ecf9ad6155c6ae9d86c2e55e17e71b01942d59eb341426df44</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:45:04+03:00</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:45:04+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>РОКИ - 80 ЕООД</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>206188017</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>ФтЕЦ "Роки 5"</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Плевен</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Долна Митрополия</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Тръстеник</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>73359</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>26.06.2026</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>Слънчева енергия</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>d29883280650b4defcd765d0dea90a6d0ab31a996f8bd22b5158d72bb038b92a</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:45:04+03:00</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:45:04+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>НП Минкови ЕООД</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>207219493</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>ФтЕЦ "НП Минкови - Граф Игнатиево"</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Пловдив</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Марица</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Граф Игнатиево</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>17806</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>0.46864</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>08.07.2026</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>Слънчева енергия</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>9ff036fadac5e645493f5bf4a07e5c5a195e3f8973b7a148dc58c6b575667bce</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:45:04+03:00</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:45:04+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>АВИС ИНЖЕНЕРИНГ ЕООД</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>115011904</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>ФтЕЦ "Авис Инженеринг - Пловдив"</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Пловдив</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Пловдив</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Пловдив</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>56784</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>0.13978</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>11.05.2026</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>Слънчева енергия</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>8aa1774e85b995916c200deffec1a39f20e636bccb7e55ca040090259346df51</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:45:04+03:00</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:45:04+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>СОЛАР ИИ ЕООД</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>207237616</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>ФтЕЦ "Екострой 2 - Раковски"</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Пловдив</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Раковски</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Раковски</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>62075</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>0.2065</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>15.07.2025</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>Слънчева енергия</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>d50acb979857633959a0fb2c17b7a32387212f2d0e276ea325c0c21d455305f8</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:45:04+03:00</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:45:04+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Булсан Ямбол 1 ЕООД</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>206863649</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>ФтЕЦ "Булсан Ямбол 1 -Ямбол"</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Ямбол</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Ямбол</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Ямбол</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>87374</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>20.03.2025</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>Слънчева енергия</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>264ab07176ed360fcb6e3b0a29df31d8f4bd5b3af12f1847361df3ffc48bef19</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:45:04+03:00</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:45:04+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Донатекс и Ко ЕООД</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>115107055</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>ФтЕЦ "Донатекс - Сушица"</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Пловдив</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Карлово</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Карлово</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>36498</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>3.0038</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>13.05.2026</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>Слънчева енергия</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>c9e0c31e32c13db4b2903b3f83a43e6a22ce77d211c9a3635534d3eca06152be</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:45:04+03:00</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:45:04+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>МАЛЕНОВО СОЛАР ООД</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>200654831</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>ФтЕЦ "Маленово - Сливен 1"</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Сливен</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Сливен</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Сливен</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>67338</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>0.1998</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>20.07.2026</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>Слънчева енергия</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>6b854eaa4133f5494dea075656c968656ecbfffe57e0009f6b1d7bf83be340e2</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:45:04+03:00</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:45:04+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>ЗЕЙНЕЛ ХЮСЕИН БОБА</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr"/>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>ФтЕЦ "Чернолик - Черно Море - 1"</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Силистра</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Дулово</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Чернолик</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>81150</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>0.015</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>29.10.2025</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>Слънчева енергия</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>5d2e28cf0cf23f9f9b1accd010ee772cf89882dcda36c0979a76f1fe25f65bb8</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:45:04+03:00</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:45:04+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>"БИО ТРЕЕ" ЕООД</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>203774259</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>ФтЕЦ "Тутраканци - 6"</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Варна</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Провадия</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Тутраканци</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>73506</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>12.06.2025</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>Слънчева енергия</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>98332515d297a2c5f4f43fdf38393ef5cf2b493fd55860c636c060370c19d2bb</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:45:04+03:00</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:45:04+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>АЛЕКС - 2015 С ЕООД</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>206846920</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>ФтЕЦ "Живодар Стойчев - Гълъбово 1"</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Стара Загора</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Гълъбово</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Гълъбово</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>18280</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>0.14762</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>01.04.2026</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>Слънчева енергия</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>5ee9fea8e97c18ed80a754d3f51f226821e239b8cdf94f5ca83b6dd9a0933655</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:45:04+03:00</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:45:04+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>"ФЕЛТИН"ООД</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>207175997</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>ФтЕЦ "Фелтин Гъмзово"</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Видин</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Брегово</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Гъмзово</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>18304</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>0.49996</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>07.07.2026</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>Слънчева енергия</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>9334bb06ece1236f48e321d60b273dff10bbdf312f25f2834448fa7fb6b4a9a3</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:45:04+03:00</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:45:04+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>ЗП ТОНЧО НИКОЛОВ ДРАГНЕВ</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>102907086</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>ФтЕЦ "Тончо Драгнев - Славянци 5"</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Бургас</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Сунгурларе</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Славянци</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>67115</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>0.08</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>03.07.2026</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>Слънчева енергия</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>fa8782ac2fe781a6782b778c0577b3afece8ab8a4ff2ae50bbe12a25e70170bd</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:45:04+03:00</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:45:04+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Фреш Тейст АД</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>203479173</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>ФтЕЦ "Варна - Владислав Варненчик -16"</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Варна</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Варна</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Варна</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>10135</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>0.33385</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>17.07.2026</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>Слънчева енергия</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>cbe52d5e7ef286342729ca26c36fb0170af3311097e87bbb025281b0e2fb20ce</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:45:04+03:00</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:45:04+03:00</t>
         </is>
       </c>
     </row>

--- a/data/new_records.xlsx
+++ b/data/new_records.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P105"/>
+  <dimension ref="A1:P78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,47 +501,47 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>НЮ ИЛЕКТРИК ПАУЪР ЕООД</t>
+          <t>М СОЛАР EООД</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>205905885</t>
+          <t>200847990</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Мокрище"</t>
+          <t>ФтЕЦ "М Солар - Медвен"</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Пазарджик</t>
+          <t>Сливен</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Пазарджик</t>
+          <t>Котел</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Мокрище</t>
+          <t>Медвен</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>48876</t>
+          <t>47528</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>29.11.2011</t>
+          <t>19.07.2011</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -554,64 +554,64 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>06de05a2b321f77b8bb9930b2b3a146876c4310c9960feddba33e8e55c4a9b6f</t>
+          <t>24bb5643026c29954fd769b45a88ebd5d602d8a43c320fc983d00e8d656a2025</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>НЮ ИЛЕКТРИК ПАУЪР ЕООД</t>
+          <t>МД СОЛАР EООД</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>205905885</t>
+          <t>200920082</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Еспе Енерджи"</t>
+          <t>ФтЕЦ "МД Солар - Медвен"</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Плевен</t>
+          <t>Сливен</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Гулянци</t>
+          <t>Котел</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Милковица</t>
+          <t>Медвен</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>48204</t>
+          <t>47528</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>28.06.2012</t>
+          <t>21.04.2012</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -624,64 +624,64 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>d31326de31ae2f3b5a1ae1375637dd84d1559ff845a0181d428edd7480a86bcc</t>
+          <t>107184d25a56d10eff1a1f6cd8eed407c034cb8ddade140f986fc5015486ae5a</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ЕТ ЕЛМИРА ГЕОРГИЕВА - ИЧИ</t>
+          <t>МН СОЛАР EООД</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>121230653</t>
+          <t>200959078</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Долна баня"</t>
+          <t>ФтЕЦ "МН Солар - Медвен"</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>София-Област</t>
+          <t>Сливен</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Долна баня</t>
+          <t>Котел</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Долна баня</t>
+          <t>Медвен</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>22006</t>
+          <t>47528</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.18424</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>12.10.2012</t>
+          <t>29.06.2012</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -694,64 +694,64 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>04d42ac29e2eee46ff0e480fb1433dd8acaceb5056fc8c65a18addabe8913300</t>
+          <t>9dcb8fafb62bf43b056b6027f880bbe67bc6bbce76ab15fa49ca118168475d97</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>БОСОЛАР ЕООД</t>
+          <t>Мелком Енерджи ЕООД</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>200622591</t>
+          <t>201587346</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Енвиво 4 - Зетьово"</t>
+          <t>ФтЕЦ "Мелком - Крушаре"</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Стара Загора</t>
+          <t>Сливен</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Чирпан</t>
+          <t>Сливен</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Зетьово</t>
+          <t>Крушаре</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>30819</t>
+          <t>40083</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.19941</t>
+          <t>0.85536</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>08.06.2012</t>
+          <t>28.06.2012</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -764,54 +764,54 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>9196e3b3e64d2ffab4f71b7b741c1327da356dc26c75bc6c8be271e34b80e912</t>
+          <t>a17ced2fa6bb2d36fce9f5461e8ca1561ec23ce1328ef69aee0570470c74ef4d</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>МИЗАН ЕООД</t>
+          <t>Бул Инвест 25 ЕООД</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>201389300</t>
+          <t>208627722</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Мизан - Крумовград"</t>
+          <t>ФтЕЦ "Елит Газ - Бинкос 1"</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Кърджали</t>
+          <t>Сливен</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Крумовград</t>
+          <t>Сливен</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Крумовград</t>
+          <t>Бинкос</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>39970</t>
+          <t>4114</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>21.12.2013</t>
+          <t>01.04.2020</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -834,64 +834,64 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>b1448f1e135c375ec24b151327f491de60e7be0edc42d812d818e7f52503e870</t>
+          <t>7287c2eeecb9a447a3ee496e1da79d13d70d5aa0a4a8bca006dc32c47c7a3d57</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>СТЕФАНОВИ ООД</t>
+          <t>ТРИ ИНВЕСТ ЕООД</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>102860238</t>
+          <t>119656471</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ВтЕЦ "Стефанови 2 - Зетьово"</t>
+          <t>ФтЕЦ "Глогинка - 3"</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Бургас</t>
+          <t>Търговище</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Айтос</t>
+          <t>Попово</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Зетьово</t>
+          <t>Глогинка</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>30805</t>
+          <t>15103</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>15.09.2014</t>
+          <t>04.06.2020</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -899,72 +899,76 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Вятърна енергия</t>
+          <t>Слънчева енергия</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>1e247143cc5f9ee754323c49c2b1fc17c71f9ead778eb12b849e52b24bb437fd</t>
+          <t>c49f629c94d3a4152b096dc76af2909eeeb100c62ea013e56498e1b8b4f09c4b</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>СТУДИО МАЯ ЕООД</t>
+          <t>ТОНИ АН 02 ЕООД</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>131021997</t>
+          <t>206070057</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Студио Мая"</t>
+          <t>ФтЕЦ "Изворче"</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Благоевград</t>
+          <t>Ловеч</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Гърмен</t>
+          <t>Ловеч</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Гърмен</t>
+          <t>Изворче</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>18366</t>
+          <t>32500</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>23.27825</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>01.10.2015</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+          <t>01.11.2025</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>01.10.2020</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
@@ -974,54 +978,54 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>3d615a32783c98cc82f857adb3d84b751aec3af0801298824b9cc743d9fa8c0f</t>
+          <t>ab48faedc0bf3d72cc8bda86ef1daf8246f89d1567032f003cd25b508537534e</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ЦМ Еделвайс комфорт ООД</t>
+          <t>СНЕД ЕООД</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>205450479</t>
+          <t>205767982</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Иваново - 1"</t>
+          <t>ФтЕЦ "Снед - Свобода 1"</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Русе</t>
+          <t>Стара Загора</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Иваново</t>
+          <t>Чирпан</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Иваново</t>
+          <t>Свобода</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>32095</t>
+          <t>65810</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1031,7 +1035,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>28.09.2020</t>
+          <t>10.06.2021</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -1044,64 +1048,64 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2c0d71f4b52ef2fe2b6b2a223562564cb569febdf0a434bb0f03cbaad55ad7d5</t>
+          <t>74d5b340bda475f515d4fd0a7c30fb60f4a3666b8a3ab5fc73580d6e3f8249d7</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ЗП ТОНЧО НИКОЛОВ ДРАГНЕВ</t>
+          <t>Бул Инвест 25 ЕООД</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>102907086</t>
+          <t>208627722</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Тончо Драгнев - Чубра 2"</t>
+          <t>ФтЕЦ "Елит Газ - Бинкос 2"</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Бургас</t>
+          <t>Сливен</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Сунгурларе</t>
+          <t>Сливен</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Чубра</t>
+          <t>Бинкос</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>81582</t>
+          <t>4114</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.0297</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>22.07.2021</t>
+          <t>15.07.2021</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -1114,34 +1118,34 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>d5a955882a9b2dfa3d2bbe3533f3de181305acc276942b4b7952a05d4b8a69cd</t>
+          <t>0e724f644fb3b4dbedad6f6f8c497a2806e149859e79193d7f6f8cf4447acdcd</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ЗП ТОНЧО НИКОЛОВ ДРАГНЕВ</t>
+          <t>Бул Инвест 25 ЕООД</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>102907086</t>
+          <t>208627722</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Тончо Драгнев - Чубра 3"</t>
+          <t>ФтЕЦ "Елит Газ - Деветинци 1"</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1151,27 +1155,27 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Сунгурларе</t>
+          <t>Карнобат</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Чубра</t>
+          <t>Деветинци</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>81582</t>
+          <t>20448</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.0297</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>22.07.2021</t>
+          <t>15.04.2021</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
@@ -1184,34 +1188,34 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>5b5f6acdaec9eaa7e26fa073a1a2eb077bfd3b44ee7f863e6bbb42bab0f84988</t>
+          <t>b3c89dac6e749f6c55330e7e6556aba43ccd859c5c1c10f838bf3289fe6aca1a</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ЗП ТОНЧО НИКОЛОВ ДРАГНЕВ</t>
+          <t>Бул Инвест 25 ЕООД</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>102907086</t>
+          <t>208627722</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ФтЕЦ " Драгнев - Славянци 2"</t>
+          <t>ФтЕЦ "Елит газ - Деветинци 2"</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1221,27 +1225,27 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Сунгурларе</t>
+          <t>Карнобат</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Славянци</t>
+          <t>Деветинци</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>67115</t>
+          <t>20448</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.0297</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>29.10.2021</t>
+          <t>21.06.2021</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -1254,34 +1258,34 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>b2c6ddd5cbe361457ede9cfd22a988c7ca73cc8abac5c8e5a462339dd078cebe</t>
+          <t>eebf20e3b7b2e257db7b4340c67245e81a54185ad8e0a3014e67fdb58594ce0d</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ЗП ТОНЧО НИКОЛОВ ДРАГНЕВ</t>
+          <t>Бул Инвест 25 ЕООД</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>102907086</t>
+          <t>208627722</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ФтЕЦ " Драгнев - Славянци 1"</t>
+          <t>ФтЕЦ "Елит газ - Церковски 1"</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1291,27 +1295,27 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Сунгурларе</t>
+          <t>Карнобат</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Славянци</t>
+          <t>Церковски</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>67115</t>
+          <t>78416</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.0297</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>22.07.2021</t>
+          <t>12.07.2021</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -1324,34 +1328,34 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>d04c59e04c64f22c2cc1f240cae900a5696d21a03662c171aff92c97c9aef2d5</t>
+          <t>32074310ea246d1fc58ada8815a30ced469ea264fe46ef9e89bbcee8f670e319</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ЗП ТОНЧО НИКОЛОВ ДРАГНЕВ</t>
+          <t>Бул Инвест 25 ЕООД</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>102907086</t>
+          <t>208627722</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Тончо Драгнев - Чубра 1"</t>
+          <t>ФтЕЦ "Елит Газ - Церковски 2"</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1361,17 +1365,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Сунгурларе</t>
+          <t>Карнобат</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Чубра</t>
+          <t>Церковски</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>81582</t>
+          <t>78416</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1381,7 +1385,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>11.03.2021</t>
+          <t>01.12.2021</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -1394,54 +1398,54 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>6053e8f88b90ddf28e824d07b963cea5aa1f4a6ea4892befcfab27dd1fcdbdf5</t>
+          <t>25717d848b9637c31f2905948a1426a12c0dc600c5324e7e66c1f9ca59a080f4</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>МИЗАН ЕООД</t>
+          <t>Бул Инвест 25 ЕООД</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>201389300</t>
+          <t>208627722</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Мизан - Свирачи"</t>
+          <t>ФтЕЦ "Елит газ - Каменово 1"</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Хасково</t>
+          <t>Сливен</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ивайловград</t>
+          <t>Нова Загора</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Свирачи</t>
+          <t>Каменово</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>65704</t>
+          <t>35907</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1451,7 +1455,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>22.05.2021</t>
+          <t>10.09.2021</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -1464,64 +1468,60 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>3561dfdaf5a639eb2b771935824e9f1b901ced8067a2878528a33d6a95ce46ea</t>
+          <t>d8c6be1afd909a13aebc16c5c50289fbb186a65405a9bdf3ab4648f08c70e1fd</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ХАЙ ТЕК СЕРВИЗ ООД</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>202927894</t>
-        </is>
-      </c>
+          <t>ИВАН КАЛИНОВ ГАНЧЕВ</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ФЕЦ ЛЕДЕНИК 2</t>
+          <t>ФтЕЦ "Иван Ганчев - Каравелово"</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Велико Търново</t>
+          <t>Пловдив</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Велико Търново</t>
+          <t>Карлово</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Велико Търново</t>
+          <t>Каравелово</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>10447</t>
+          <t>36186</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.02992</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>18.01.2022</t>
+          <t>27.07.2021</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -1534,17 +1534,17 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>5247510900c59bc6fa10cdb8e90fe75d544c734a07e34245341689ff4802d344</t>
+          <t>70baa876bb3dc941cb4a4f97cf109a6b8850c0730a202c93d211ea4214134890</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Ковачевец - 8"</t>
+          <t>ФтЕЦ "Иванча - Търговище"</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1576,22 +1576,22 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ковачевец</t>
+          <t>Иванча</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>37469</t>
+          <t>32189</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.02975</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>24.06.2021</t>
+          <t>20.05.2021</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -1604,64 +1604,60 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>9f5512a21e929285084744fca22a27edebb7905e6a2bce378bce54ccd38810ae</t>
+          <t>f7a3b25e901b0894794462161c81821d9e976fc5bf4d49f9144046f5df88a1aa</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ТРИ ИНВЕСТ ЕООД</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>119656471</t>
-        </is>
-      </c>
+          <t>Венелин Вълчев Нейков</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Садина - 9"</t>
+          <t>ФтЕЦ "Зайчино ореше - 1"</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Търговище</t>
+          <t>Шумен</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Попово</t>
+          <t>Нови пазар</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Садина</t>
+          <t>Зайчино ореше</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>65067</t>
+          <t>30274</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.02975</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>20.05.2021</t>
+          <t>14.10.2021</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
@@ -1674,64 +1670,64 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>83e9781dbbd5728a1c9d80de903a4fce15c853d63d1cce66dacf35a8eba636cb</t>
+          <t>b4be715574cfbeff9114f743e2055562440d08c06c42efba3e24ca327cd47b61</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ТРИ ИНВЕСТ ЕООД</t>
+          <t>Бул Инвест 25 ЕООД</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>119656471</t>
+          <t>208627722</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Паламарца - 5"</t>
+          <t>ФтЕЦ "Елит газ - Церковски 3"</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Търговище</t>
+          <t>Бургас</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Попово</t>
+          <t>Карнобат</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Паламарца</t>
+          <t>Церковски</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>55213</t>
+          <t>78416</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.02975</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>24.06.2021</t>
+          <t>17.01.2022</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
@@ -1744,64 +1740,60 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>f9934ae8bd537d651f8d92d001e49a328bcbdb6330d86b96585dc3baa4684caa</t>
+          <t>430334e81495db72b8da38119a1c74cacf7a186a1189bbd82b8b3325dac9d721</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ТРИ ИНВЕСТ ЕООД</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>119656471</t>
-        </is>
-      </c>
+          <t>Димитър Герасимов Тасев</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Кьосевци"</t>
+          <t>ФтЕЦ "Димитър Тасев"</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Търговище</t>
+          <t>Благоевград</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Антоново</t>
+          <t>Кресна</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Кьосевци</t>
+          <t>Кресна</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>41099</t>
+          <t>14492</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.02975</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>20.05.2021</t>
+          <t>01.06.2022</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
@@ -1814,64 +1806,64 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>656c25c91579d8aee93d6379cad325a01bba7dc67d6b4484eb01d56bb370ca24</t>
+          <t>6b4afda379fdc636db2491dcb138b228892d43bde8df66e758224cacafa825d1</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ТРИ ИНВЕСТ ЕООД</t>
+          <t>Бул Инвест 25 ЕООД</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>119656471</t>
+          <t>208627722</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Ломци"</t>
+          <t>ФтЕЦ "Елит газ - Зимница 1"</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Търговище</t>
+          <t>Ямбол</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Попово</t>
+          <t>Стралджа</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ломци</t>
+          <t>Зимница</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>44286</t>
+          <t>30898</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.02975</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>20.05.2021</t>
+          <t>01.03.2022</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
@@ -1884,67 +1876,71 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2378aaa1b7a87b505de582be33850085905a369c665f160511fde253e9c05f57</t>
+          <t>bb2f2dbdd7d442fb5030dbd7070829ecd41ebb568f191ce048b0c0f50a138308</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ТРИ ИНВЕСТ ЕООД</t>
+          <t>БЕНТЛИ ГРИЙН ЕНЕРДЖИ ООД</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>119656471</t>
+          <t>206336629</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Манастирица"</t>
+          <t>ФтЕЦ "Димитър Братанов - Бориславци 6"</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Търговище</t>
+          <t>Хасково</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Попово</t>
+          <t>Маджарово</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Манастирица</t>
+          <t>Бориславци</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>47007</t>
+          <t>5503</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.1996</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>20.05.2021</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
+          <t>01.01.2025</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>24.11.2022</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
@@ -1954,64 +1950,60 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>f48c748104070ec3001bb1d61a55895fa41dd4ae8a52ee3ed4a1ab8ea12959ef</t>
+          <t>0b982a1d9b12c0631a9d34ef7ac9386be90fae21a29961b2111f4d8ae3ef2d5f</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>АМИЧИ ООД</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>121000823</t>
-        </is>
-      </c>
+          <t>Руско Господинов Койчев</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Амичи"</t>
+          <t>ФтЕЦ " Руско Койчев - Драганци 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Кюстендил</t>
+          <t>Бургас</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Дупница</t>
+          <t>Карнобат</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Дупница</t>
+          <t>Драганци</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>68789</t>
+          <t>23176</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.07975</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>23.08.2026</t>
+          <t>04.02.2026</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
@@ -2024,67 +2016,71 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>568e1d52258498b9a9367702ee27cfb32fa8bd7c18a68d488519c91d93ebce96</t>
+          <t>f8e8aa38833b85391281af48395b0ccb5ea5349393e978129b0f180efecf879f</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>САВ-РАЗГРАД ООД</t>
+          <t>БЕЛОЗЕМ СОЛАР ПАРК 3 ЕООД</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>200425074</t>
+          <t>205978399</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Разград - Перистър"</t>
+          <t>ФтЕЦ "Верила"</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Разград</t>
+          <t>Кюстендил</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Разград</t>
+          <t>Дупница</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Разград</t>
+          <t>Крайници</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>61710</t>
+          <t>39339</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>21.10.2021</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
+          <t>30.03.2026</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>07.04.2023</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
@@ -2094,54 +2090,54 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>dbbf2b06a9ef1a1c4eee227bb618cdb9d1d101473361493f8de5ca63d181799b</t>
+          <t>2f060018b8479d402f583f23fcc9152c4ee5530228671c0b6b00a064a1a6c11e</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>БЕЛСИСТЕМС ООД</t>
+          <t>ГЕОМАР - 21 ЕООД</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>117522513</t>
+          <t>206357299</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Бяла-Русе-Хан Аспарух"-Закрит обект</t>
+          <t>ФТЕЦ "Войника - Джоди Енерджи 1"</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Русе</t>
+          <t>Ямбол</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Бяла</t>
+          <t>Стралджа</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Бяла</t>
+          <t>Войника</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>7603</t>
+          <t>11908</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2151,7 +2147,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>01.01.2022</t>
+          <t>07.03.2023</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
@@ -2164,67 +2160,71 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>d7bfd5d4668ed73e24862bc6946b33b62f6ec768423078574aeb6b9db64fe991</t>
+          <t>dd8a04922f776c2201fdad6f62d737d5abd158cc3982f32ba38b3e7c4c2f2adf</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>БОГИ - 6 ООД</t>
+          <t>МЕТАЛ ПАРТНЕРС ГРУП ООД</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>102870243</t>
+          <t>160070303</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Боги 6 - Бургас"</t>
+          <t>ФтЕЦ "Метал Партнерс - Сопот"</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Бургас</t>
+          <t>Пловдив</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Бургас</t>
+          <t>Сопот</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Бургас</t>
+          <t>Сопот</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>7079</t>
+          <t>68080</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>23.356295</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>15.09.2022</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
+          <t>31.08.2026</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>10.08.2023</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
@@ -2234,64 +2234,64 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>94389017ef5eda6d419fa2aeef90430cf2f517a0a9777c3738b022fe4e5570a8</t>
+          <t>43fca98ee8833c2f1bc8e00b62e100aa6674403fa8cd705d75ab6784294329f8</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ВОРТЕКС ВВ ЕООД</t>
+          <t>Инчкейп Балканс ЕООД</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>200857963</t>
+          <t>204421080</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Вортекс ВВ - Априлово"</t>
+          <t>ФтЕЦ "Силвър Стар - Бенковски"</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Стара Загора</t>
+          <t>Пловдив</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Гълъбово</t>
+          <t>Марица</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Априлово</t>
+          <t>Бенковски</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>3839</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0.0297</t>
+          <t>0.389675</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>19.04.2022</t>
+          <t>10.10.2023</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
@@ -2304,60 +2304,64 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>90a7becd14fec4412d5e85a5619b2addf343e5ec9745263d8c4dfc42a5a1c730</t>
+          <t>39b79a45ab2f3f41b55519df68fac06622e70ad986d073a031b0baf15beca739</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Владимир Йорданов Манолов</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
+          <t>ЕЛИТ ЕНЕРДЖИ 2025 ЕООД</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>208627715</t>
+        </is>
+      </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Силистра - Васил Левски"-Закрит обект</t>
+          <t>ФтЕЦ "Елит Газ - Роза"</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Силистра</t>
+          <t>Ямбол</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Силистра</t>
+          <t>Тунджа</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Силистра</t>
+          <t>Роза</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>66425</t>
+          <t>62921</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>16.08.2022</t>
+          <t>07.07.2021</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
@@ -2370,64 +2374,64 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>26de54eee02ee00a45fda5a904ddf48bcb3abbf63f41b67d67a4a7e85f446e1e</t>
+          <t>dfd4cbdf43ec15fa1cbfdc3e286f009050ec7a62258d43873d219c2795d5c909</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>РВК 1 ЕООД</t>
+          <t>ТБГ КОНСУЛТ ЕООД</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>200742345</t>
+          <t>175284380</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Калев Сух.чешма"</t>
+          <t>ФтЕЦ "ТБГ Консулт - Априлово 5"</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Сливен</t>
+          <t>Стара Загора</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Сливен</t>
+          <t>Гълъбово</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Сливен</t>
+          <t>Априлово</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>67338</t>
+          <t>552</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>198.8</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>26.09.2022</t>
+          <t>17.08.2023</t>
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
@@ -2440,64 +2444,64 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2e16fbb8085312935f601762783b9904b7dc87c03bbd6105f6da2113d07fc761</t>
+          <t>da333b84e12970f3d9092c4fbf8d88aef864c3a5ee27c26b59dd84936f8c2edb</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>КОЗЛОДУЙ ООД</t>
+          <t>ВИКТОРИЯ МКМ ООД</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>812212481</t>
+          <t>200084057</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Козлодуй - Бургас"</t>
+          <t>ФтЕЦ "Каварна - Г. С. Раковски"</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Бургас</t>
+          <t>Добрич</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Бургас</t>
+          <t>Каварна</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Бургас</t>
+          <t>Каварна</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>7079</t>
+          <t>35064</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>0.199</t>
+          <t>0.0387</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>01.02.2023</t>
+          <t>17.07.2026</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
@@ -2510,54 +2514,54 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>a015802477f5a636decff777f01b94580ef3e343e564cd8de41980617547e7c1</t>
+          <t>505bfa9ee2169a02c43464a37a05575f669cd34bf4fb2d637cb9ae88d33df2b8</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ЗП ТОНЧО НИКОЛОВ ДРАГНЕВ</t>
+          <t>АСЯ ЛАЗАРОВА АТАНАСОВА</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>102907086</t>
+          <t>181001463</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ФтЕЦ" Тончо Драгнев - Славянци 3"</t>
+          <t>ФтЕЦ "Калугерица"</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Бургас</t>
+          <t>Шумен</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Сунгурларе</t>
+          <t>Каспичан</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Славянци</t>
+          <t>Каспичан</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>67115</t>
+          <t>36590</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2567,7 +2571,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>17.01.2023</t>
+          <t>24.02.2023</t>
         </is>
       </c>
       <c r="J31" t="inlineStr"/>
@@ -2580,67 +2584,67 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>9cf9ea0812f734e95cdff5b87c9c7c60b241026a7fb99e2e13c8ec4e0c92089d</t>
+          <t>ab51d02f9a4fd2b3c3340404917e8e00b584e6b096309e3f60dfa64e3740d9ad</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Джи Ем Сън Систем Солар ЕООД</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>206684272</t>
-        </is>
-      </c>
+          <t>Капка Бойчова Йорданова</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Алфатар - Димитър Талев"</t>
+          <t>ФтЕЦ "Капка Йорданова"</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Силистра</t>
+          <t>Перник</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Алфатар</t>
+          <t>Земен</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Алфатар</t>
+          <t>Земен</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>415</t>
+          <t>30778</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.0396</t>
+          <t>540.0297</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>01.02.2023</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr"/>
+          <t>25.09.2026</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>03.05.2023</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
@@ -2650,67 +2654,71 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>b2caa24cec7ea4c8890ce37dfe9d45dc1a95413f7976908068142fc0f5620099</t>
+          <t>647aa4c99b5f7bf066259bf9dcd287c564890f8ce7154fc1dea98b1a918312e4</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ТРИТОН ЕНЕРДЖИ ЕООД</t>
+          <t>АМИГО 99 ООД</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>206147963</t>
+          <t>203706240</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Тритон 6"</t>
+          <t>ФтЕЦ"Амиго 99-Ковачите 1"</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Плевен</t>
+          <t>Сливен</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Гулянци</t>
+          <t>Сливен</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Милковица</t>
+          <t>Ковачите</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>48204</t>
+          <t>37530</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>23.54352</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>27.03.2023</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr"/>
+          <t>05.09.2023</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>10.07.2023</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
@@ -2720,64 +2728,64 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>5405a91845462585663e6aba5be177c05f8d671d0227e75d9752e7282eea83ae</t>
+          <t>5b87e0ea8d675baf2558aa64db1a108944f10d55b5073b3a11f4e5b785f09046</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ВАНИС 03 ООД</t>
+          <t>Жан Захариев ЕООД</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>207074083</t>
+          <t>207258763</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Ванис"</t>
+          <t>ФТЕЦ" Жан Захариев"</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Плевен</t>
+          <t>Кюстендил</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Долна Митрополия</t>
+          <t>Кочериново</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Тръстеник</t>
+          <t>Пороминово</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>73359</t>
+          <t>57830</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.02997</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>01.06.2023</t>
+          <t>20.12.2023</t>
         </is>
       </c>
       <c r="J34" t="inlineStr"/>
@@ -2790,60 +2798,60 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>5271887b092ec62d7f87bbb1cb53436e5bbee30846dfac9493a609ac57a05fa0</t>
+          <t>574198942e75c2cc119662d340a13f3c51052fb06fa99a6caecaf6800c4f267e</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Ирена Жоресова Хаджиева</t>
+          <t>БИЛЯНА МИРЧЕВА ИЛИЕВА</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Градище - Габрово - 1"</t>
+          <t>ФтЕЦ "Айдемир - София - 3"</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Габрово</t>
+          <t>Силистра</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Севлиево</t>
+          <t>Силистра</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Градище</t>
+          <t>Айдемир</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>17542</t>
+          <t>895</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0.014715</t>
+          <t>0.015</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>15.06.2023</t>
+          <t>17.02.2023</t>
         </is>
       </c>
       <c r="J35" t="inlineStr"/>
@@ -2856,64 +2864,64 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>d979194fb02fa4df11db4bb408669ef75ddf49e4475af9f008c52b749e9728f3</t>
+          <t>583a77c6ab24d93c5306292f7d02070a2f60f1a4fbe08c3bf1b46bb2fcff4008</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>"СОЛАРСИМО" - ЕООД</t>
+          <t>ЕЛИТ ЕНЕРДЖИ 2025 ЕООД</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>201372030</t>
+          <t>208627715</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Тренев и Синове"</t>
+          <t>ФтЕЦ "Елит газ -Каравелово"</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Благоевград</t>
+          <t>Ямбол</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Сандански</t>
+          <t>Тунджа</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Склаве</t>
+          <t>Каравелово</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>66785</t>
+          <t>36200</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0.5661</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>24.04.2024</t>
+          <t>08.07.2024</t>
         </is>
       </c>
       <c r="J36" t="inlineStr"/>
@@ -2926,34 +2934,30 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>b449472e2e2d9fbbc6d3efa3741711f1861de4727ed7799b52e8b13c6eb47619</t>
+          <t>5d2093510bcc7c7c558697bbe21e0eada411f7be12eef5a1faecccdde3e3aa65</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Селекта ММ</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>204457404</t>
-        </is>
-      </c>
+          <t>Делчо Колев Колев</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Селект ММ - Крепост"</t>
+          <t>ФтЕЦ "Делчо Колев - Върбица 2"</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2968,29 +2972,25 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Крепост</t>
+          <t>Върбица</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>39668</t>
+          <t>76087</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2.37115</t>
+          <t>0.029475</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>20.03.2026</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>28.05.2024</t>
-        </is>
-      </c>
+          <t>19.12.2023</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
@@ -3000,64 +3000,64 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>53d53122a13cf472bcdd4a8ed3d93ab689f2358993b0392cf1d74cedd190569a</t>
+          <t>628455af3031ebcf7010c4c73019dd4f5c716553d88856cd263ade036894953b</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>АЛУМИНА ЕЛИТ 2003 ЕООД</t>
+          <t>ЕВРОПЕТРОЛ ЕООД</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>104612589</t>
+          <t>102636724</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Велико Търново - Дълга Лъка - 2"</t>
+          <t>ФтЕЦ "Европетрол - Бургас 2"</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Велико Търново</t>
+          <t>Бургас</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Велико Търново</t>
+          <t>Бургас</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Велико Търново</t>
+          <t>Бургас</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>10447</t>
+          <t>7079</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>16.05.2024</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
@@ -3070,64 +3070,64 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>915f50162cbfcaa7c6ea351c1dcb9ba9eb94a396380fea6affd5c5e763a547ca</t>
+          <t>6e5e9e2257a64b40403fb36e07355c790e57daafae21a5ccf99dcc5e9a9bfc9a</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>БРИТ ТРЕЙД ЕООД</t>
+          <t>ЕВРОПЕТРОЛ ЕООД</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>206825851</t>
+          <t>102636724</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Брит Трейд - Граф Игнатиево 1"</t>
+          <t>ФтЕЦ "Европетрол - Бургас 1"</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Пловдив</t>
+          <t>Бургас</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Марица</t>
+          <t>Бургас</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Граф Игнатиево</t>
+          <t>Бургас</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>17806</t>
+          <t>7079</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>02.10.2023</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="J39" t="inlineStr"/>
@@ -3140,64 +3140,64 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>549a739694c90ad040ca024ec4efe186fb2029edf302dbf1b9c5b927796d7287</t>
+          <t>395aeeaaef4555b0e59fb3b74eb350d290f4cede31f3cfe6147fc20274e07690</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Елисей Тех ЕООД</t>
+          <t>ПОЛИГРУП ООД</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>204431982</t>
+          <t>115353345</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Елисей тех"</t>
+          <t>ФтЕЦ "ПОЛИГРУП"</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Плевен</t>
+          <t>Пловдив</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Кнежа</t>
+          <t>Асеновград</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Кнежа</t>
+          <t>Асеновград</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>37376</t>
+          <t>702</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>15.08.2024</t>
+          <t>06.06.2025</t>
         </is>
       </c>
       <c r="J40" t="inlineStr"/>
@@ -3210,64 +3210,64 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>b25abb7c17e6b20f51485c8f463672e492507c1b0b125435c016af88e1ecac98</t>
+          <t>1b63b9cd8cb4febda636cba393ab136cc88d2677c89c6d771c4030dfafa76e89</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>КРИСТАЛ ГЛАС-ХОЛДИНГ АД</t>
+          <t>Петрови Солар 2021 ЕООД</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>206062669</t>
+          <t>206399622</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Дивдядово - Велики Преслав - 2"</t>
+          <t>ФтЕЦ "Петрови солар"</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Шумен</t>
+          <t>Благоевград</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Шумен</t>
+          <t>Благоевград</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Шумен</t>
+          <t>Обел</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>83510</t>
+          <t>53031</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>0.1991</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>02.10.2024</t>
+          <t>26.09.2025</t>
         </is>
       </c>
       <c r="J41" t="inlineStr"/>
@@ -3280,60 +3280,64 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>93791dbfec7445792cc88f62ab3ebb355f4aec3fcacf20f6fca2ad29c4a9fe1e</t>
+          <t>8216764b79708afbb6287fe5ed7ef481a560afe59b8eed9c851d7fdbbe256bef</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Борислав Любомиров Илиев</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr"/>
+          <t>ДАТАНЕТ ООД</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>104655634</t>
+        </is>
+      </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Борислав Илиев"</t>
+          <t>ФтЕЦ "Датанет"</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>София-град</t>
+          <t>Велико Търново</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Столична</t>
+          <t>Свищов</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Нови Искър</t>
+          <t>Деляновци</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>20630</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0.0297</t>
+          <t>0.29892</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>20.12.2023</t>
+          <t>18.09.2025</t>
         </is>
       </c>
       <c r="J42" t="inlineStr"/>
@@ -3346,60 +3350,64 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>d5b0a95b8a5ff210bbb65dae856b64801974a2f2ba86943a7568622496a8f95e</t>
+          <t>7d26e64d6b397ccc48800666f41c6c612f50341f86ed6a7aac7a510ff5c8d6e3</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Стайко Тодоров Костадинов</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr"/>
+          <t>СТАНКАТ ООД</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>206811428</t>
+        </is>
+      </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Пенка Костадинова - Камено"</t>
+          <t>ФтЕЦ "Дюлино"</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Бургас</t>
+          <t>Варна</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Камено</t>
+          <t>Бяла</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Камено</t>
+          <t>Дюлино</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>35883</t>
+          <t>24739</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>0.1188</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>16.08.2024</t>
+          <t>01.10.2025</t>
         </is>
       </c>
       <c r="J43" t="inlineStr"/>
@@ -3412,63 +3420,71 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>c785809a26118c7e8c98695d1adeba203c77dfbcd22617872dfd610fc17e6a9c</t>
+          <t>4effb7dfb8182e7a5252f42525d1cf33b33a44eeac60d7ad16521f2d73fa1418</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Бисерка Георгиева Атанасова</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr"/>
+          <t>ФЕРОКОМ АД</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>115877287</t>
+        </is>
+      </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Альоша Атанасов"</t>
+          <t>ФтЕЦ "Фероком-Златитрап"</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Плевен</t>
+          <t>Пловдив</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Левски</t>
+          <t>Родопи</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Обнова</t>
+          <t>Златитрап</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>53089</t>
+          <t>31036</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.883455</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>24.07.2023</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr"/>
+          <t>10.08.2026</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>07.04.2025</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
@@ -3478,64 +3494,64 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>47d3a7a8b1e80861bc065e0aa7309757e92a9440c8962e4244f6d4618a473f3f</t>
+          <t>126386cf961f10159eb7eb9fa89d79e18150ba6631123cd9a3743c548c4827ec</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Живот в радост ЕООД</t>
+          <t>БЕЛОЗЕМ СОЛАР ПАРК 2 ООД</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>207094851</t>
+          <t>205978342</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ФтЕЦ ,,Живот в радост - Русокастро''</t>
+          <t>ФтЕЦ "Мъглиж"</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Бургас</t>
+          <t>Стара Загора</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Бургас</t>
+          <t>Мъглиж</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Бургас</t>
+          <t>Дъбово</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>7079</t>
+          <t>24342</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>0.029975</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>27.02.2024</t>
+          <t>29.08.2025</t>
         </is>
       </c>
       <c r="J45" t="inlineStr"/>
@@ -3548,63 +3564,71 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>767abcefe6343887809d6f260825b968b08e729d38f1c3d0ff68893fa7f81e81</t>
+          <t>17ca67cc21597badb0ff99a08d7832ff638e55cc70f0de51c53e2950d62098e6</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Стоянка Петрова Спирова</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr"/>
+          <t>ТЕНЕВО СОЛАР ТЕХНОЛОДЖИС ЕАД</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>206511621</t>
+        </is>
+      </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Стоянка Спирова - Оризари"</t>
+          <t>ФтЕЦ "Тенево Солар"</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Пловдив</t>
+          <t>Ямбол</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Родопи</t>
+          <t>Тунджа</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Оризари</t>
+          <t>Тенево</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>53833</t>
+          <t>72240</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>0.0276</t>
+          <t>207.6</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>01.02.2024</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr"/>
+          <t>21.05.2026</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>11.06.2025</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
@@ -3614,64 +3638,64 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>a050f8c67d6098f52f504dd85eb69ffb3d6e6bbd9048aca2f6f647273b412a3d</t>
+          <t>af2057e668678168dab31ce9bd86f34db8db2fa7e70c2973aa6fc1f5670cccc0</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>"БИО ТРЕЕ" ЕООД</t>
+          <t>ВЕНИ СОЛАР ЕООД</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>203774259</t>
+          <t>204236943</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Комарево"</t>
+          <t>ФтЕЦ "Вени солар 1"</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Варна</t>
+          <t>Плевен</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Провадия</t>
+          <t>Плевен</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Комарево</t>
+          <t>Пелишат</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>38114</t>
+          <t>55765</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.0783</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>30.01.2024</t>
+          <t>08.08.2025</t>
         </is>
       </c>
       <c r="J47" t="inlineStr"/>
@@ -3684,64 +3708,64 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>c9d6b5fc280d23d47631a6a5570ccad31a7eceb66d6c4ec7876f87255c200bca</t>
+          <t>de38f3a6e0366bcec75c7c92f34ce66d28c565280dbdf3e9a0128193cc79d96f</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>"БИО ТРЕЕ" ЕООД</t>
+          <t>АЛФА СОЛАР -Д ООД</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>203774259</t>
+          <t>207421146</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Тутраканци - 5"</t>
+          <t>ФтЕЦ "Шумен - под село"</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Варна</t>
+          <t>Шумен</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Провадия</t>
+          <t>Шумен</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Тутраканци</t>
+          <t>Шумен</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>73506</t>
+          <t>83510</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>13.03.2024</t>
+          <t>19.06.2026</t>
         </is>
       </c>
       <c r="J48" t="inlineStr"/>
@@ -3754,64 +3778,64 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>41a6c50bdd90ecf2273aa60cd76853c87ead3b2f78ccbd253d28c935dd874651</t>
+          <t>189ae7652385ed69ebdfb78eaba1421814edb3906920a441a53411852fe23475</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ЗП ТОНЧО НИКОЛОВ ДРАГНЕВ</t>
+          <t>ФСЗ ЕООД</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>102907086</t>
+          <t>207017335</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Тончо Драгнев - Славянци 4"</t>
+          <t>ФтЕЦ "Винпром Дупница"</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Бургас</t>
+          <t>Кюстендил</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Сунгурларе</t>
+          <t>Дупница</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Славянци</t>
+          <t>Дупница</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>67115</t>
+          <t>68789</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>0.19866</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>16.04.2024</t>
+          <t>28.07.2026</t>
         </is>
       </c>
       <c r="J49" t="inlineStr"/>
@@ -3824,34 +3848,34 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>113c531f3752b20639ac2b1cc8ba50d8dc7fd1dfe2d2104593d3d307a0bac256</t>
+          <t>a5127da4b1a72d8f7a1e2d84d52c841a1ffb9d38c98cd4892082c088aff0dd04</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Фонд Зелена Енергия ООД</t>
+          <t>МТТ ПРОЕКТ ЕООД</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>208722729</t>
+          <t>206859729</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Нетикс Енерджи - Малък Дол 4"</t>
+          <t>ФтЕЦ "МТТ Проект - Кравино 1"</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3861,27 +3885,27 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Братя Даскалови</t>
+          <t>Опан</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Малък дол</t>
+          <t>Кравино</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>49998</t>
+          <t>39222</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>0.1703</t>
+          <t>0.1044</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>18.07.2024</t>
+          <t>01.04.2026</t>
         </is>
       </c>
       <c r="J50" t="inlineStr"/>
@@ -3894,64 +3918,64 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>a74eec67d86bdf34cf59c5f7382f88f1f2447f05c5ed9799d81bfed5ba46c70a</t>
+          <t>669dffea78332af883536eb5da2c42c8170dcaaf88aa6e4f5467135357bf77f4</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>АПОЛОНИЯ РИЗОРТ ООД</t>
+          <t>СИСТЕМЕН АНАЛИЗ ООД</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>200180098</t>
+          <t>130992599</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Аполония ризорт - Черноморец"</t>
+          <t>ФтЕЦ "Системен Анализ - Житница 1"</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Бургас</t>
+          <t>Пловдив</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Созопол</t>
+          <t>Калояново</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Черноморец</t>
+          <t>Житница</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>81178</t>
+          <t>29475</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>11.12.2024</t>
+          <t>22.04.2026</t>
         </is>
       </c>
       <c r="J51" t="inlineStr"/>
@@ -3964,64 +3988,64 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>2551abcebff1aba6d5649444cbd21c9ffd412770c91c494dca29b1190a12cfa9</t>
+          <t>3406a6a6944392f2a6645788185a78666f43bd016227ff4a6fe90bf77b057d57</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ЕВРОПЕТРОЛ ЕООД</t>
+          <t>Булсан Ямбол 2 ЕООД</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>102636724</t>
+          <t>206863631</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Европетрол - Бургас 2"</t>
+          <t>ФтЕЦ Булсан Ямбол 2 - Ямбол</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Бургас</t>
+          <t>Ямбол</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Бургас</t>
+          <t>Ямбол</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Бургас</t>
+          <t>Ямбол</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>7079</t>
+          <t>87374</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>11.08.2026</t>
+          <t>20.03.2025</t>
         </is>
       </c>
       <c r="J52" t="inlineStr"/>
@@ -4034,64 +4058,64 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>0b430da868a33bf5285b71c58ff4b50a7a0588615a215de9e0c0d23b375958be</t>
+          <t>b0d6257e0643f72902eadb0033e4f16f0121261525643c802cac6e6f68179e54</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ЕВРОПЕТРОЛ ЕООД</t>
+          <t>ВълевИ Грийн Пауър ЕООД</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>102636724</t>
+          <t>206958015</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Европетрол - Бургас 1"</t>
+          <t>ФтЕЦ "В.Вълев - Г. Александрово 1"</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Бургас</t>
+          <t>Сливен</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Бургас</t>
+          <t>Сливен</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Бургас</t>
+          <t>Горно Александрово</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>7079</t>
+          <t>16688</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>11.08.2026</t>
+          <t>29.04.2024</t>
         </is>
       </c>
       <c r="J53" t="inlineStr"/>
@@ -4104,64 +4128,64 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>f22fd83b4e1e17e610e6d7aab2eeea6888e2aabfda6b272dbd786ef15e108df0</t>
+          <t>06866f43b2ff58515ac648b1b820096a5d09d97bcbdcecde9d87c116cacecde9</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ЕНДЮРАНС ИНВЕСТМЪНТС ЕАД</t>
+          <t>ФЕЛТИН ООД</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>208636415</t>
+          <t>207175997</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Алфасист складова база"</t>
+          <t>ФтЕЦ "Фелтин Гъмзово"</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Монтана</t>
+          <t>Видин</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Монтана</t>
+          <t>Брегово</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Монтана</t>
+          <t>Гъмзово</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>48489</t>
+          <t>18304</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>0.193855</t>
+          <t>0.49996</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>18.06.2025</t>
+          <t>07.07.2026</t>
         </is>
       </c>
       <c r="J54" t="inlineStr"/>
@@ -4174,64 +4198,64 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>4cd843bc72e83fa1708a97bb46c67e988280c598651720f7b00728c3263789ef</t>
+          <t>9fd717e8347c9b733a9be3efa4672fe7a1d85e852992422052f347fa69d352cb</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ТОМИ СИСТЪРС ООД</t>
+          <t>ПРИСАД СЪН ООД</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>206934509</t>
+          <t>207102928</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Тетово - Елин Пелин"</t>
+          <t>ФтЕЦ "Присад Сън - с. Присад"</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Русе</t>
+          <t>Бургас</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Русе</t>
+          <t>Созопол</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Тетово</t>
+          <t>Присад</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>72357</t>
+          <t>58400</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>0.0297</t>
+          <t>0.35784</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>17.01.2025</t>
+          <t>14.04.2026</t>
         </is>
       </c>
       <c r="J55" t="inlineStr"/>
@@ -4244,64 +4268,64 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>6e29bef085819356c3572fb54313de3a82c1c844de26cc7a16138e31fc2cd16c</t>
+          <t>1f8249681c1c4f504f4097aef9a5d737239ed493293871c9936d6bba8e1af38c</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>БЕЛЛ ИНВЕСТМЪНТ ЕООД</t>
+          <t>Дорис ЕООД</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>205847108</t>
+          <t>126088510</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Белл Инвестмънт - Асеновград 2"</t>
+          <t>ФтЕЦ "Дорис - Широко поле"</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Пловдив</t>
+          <t>Кърджали</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Куклен</t>
+          <t>Кърджали</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Куклен</t>
+          <t>Широко поле</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>40467</t>
+          <t>83315</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.012</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>31.07.2025</t>
+          <t>16.09.2025</t>
         </is>
       </c>
       <c r="J56" t="inlineStr"/>
@@ -4314,34 +4338,34 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>63e8a234546e1a36e6ba4d40261d2f507f328f79612298ef61788b0b4ba71231</t>
+          <t>e7f8c647a0efb5b044af45bcda6d9609be71a92f44a440e4e1143c33910bd4cf</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ЕНЕРДЖИ 83 ЕООД</t>
+          <t>АПОЛОН-В ООД</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>206017147</t>
+          <t>119603472</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Енерджи 83 - Гергевец 2"</t>
+          <t>ФтЕЦ "Аполон - Сливен 1"</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -4356,22 +4380,22 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Гергевец</t>
+          <t>Сливен</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>14800</t>
+          <t>67338</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.19872</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>16.05.2024</t>
+          <t>02.07.2026</t>
         </is>
       </c>
       <c r="J57" t="inlineStr"/>
@@ -4384,64 +4408,60 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>c51079e920e9321a1e442eb707de9266de0a4bd0d3aaafd429b1f213e4156e5b</t>
+          <t>3f9b614292ef16999def3969fbfc2a8f8cdae433cc756f6255a34aa5d16aa7fd</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ХЕЛЕКТ АД</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>202358674</t>
-        </is>
-      </c>
+          <t>Розалин Милифонов Станев</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ФтЕЦ "ПВ Алианц - Генерал Тошево"</t>
+          <t>ФтЕЦ "Дреновец 3"</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Ямбол</t>
+          <t>Видин</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Тунджа</t>
+          <t>Ружинци</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Генерал Тошево</t>
+          <t>Дреновец</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>14725</t>
+          <t>23672</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.0299</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>01.07.2025</t>
+          <t>24.04.2025</t>
         </is>
       </c>
       <c r="J58" t="inlineStr"/>
@@ -4454,60 +4474,64 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>e1a5701a725f6aad1f41a0a3ed812294a74f3da4d9c515f93358acb8003612cf</t>
+          <t>46d8c3f5013ea3a44c7aba9fc9e2c095e7de57569488db667d0869f8320ae6a6</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Ганка Тодорова Руджелева</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr"/>
+          <t>Агроинвест-94 ООД</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>126623758</t>
+        </is>
+      </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ФтЕЦ Дряновец-Разград-Гоце Делчев</t>
+          <t>ФтЕЦ "Агроинвест - Нова Надежда"</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Разград</t>
+          <t>Хасково</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Разград</t>
+          <t>Хасково</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Дряновец</t>
+          <t>Нова Надежда</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>23902</t>
+          <t>51891</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.0297</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>31.03.2025</t>
+          <t>16.09.2022</t>
         </is>
       </c>
       <c r="J59" t="inlineStr"/>
@@ -4520,60 +4544,64 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>ca7e8994d38b5dd69b790244563bfab94693a0048782c54b52eceb39409c8fed</t>
+          <t>9f68e85c365bef6f610f5397235402e59f13a1167b371eb67fe3d6c76a17354c</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Стайко Тодоров Костадинов</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr"/>
+          <t>Милчев ЕООД</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>123682098</t>
+        </is>
+      </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Стайко Костадинов - Камено"</t>
+          <t>ФтЕЦ "Милчев - Чирпан 1"</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Бургас</t>
+          <t>Стара Загора</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Камено</t>
+          <t>Чирпан</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Камено</t>
+          <t>Чирпан</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>35883</t>
+          <t>81414</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.199</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>01.09.2025</t>
+          <t>17.07.2026</t>
         </is>
       </c>
       <c r="J60" t="inlineStr"/>
@@ -4586,64 +4614,64 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>ab49c182cab638c5ac8363555c80c41ac7d75d70a2b0fe76d4da30303b4f72f9</t>
+          <t>4405ee84634bc3d53d2a86aa8a2640f29764ce33e9c15545190533c6b2a96c55</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ЕТ ШАНС-МИЛКО БАЙЧЕВ</t>
+          <t>БЕЛСИСТЕМС ООД</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>104040064</t>
+          <t>117522513</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Поликраище - Ивайло - 1"</t>
+          <t>ФтЕЦ "Бяла - Русе - Никола Й. Вапцаров - 1"</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Велико Търново</t>
+          <t>Русе</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Горна Оряховица</t>
+          <t>Бяла</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Поликраище</t>
+          <t>Бяла</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>57217</t>
+          <t>7603</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>12.09.2025</t>
+          <t>15.06.2026</t>
         </is>
       </c>
       <c r="J61" t="inlineStr"/>
@@ -4656,71 +4684,67 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>fbc6a05909658977aaad460283c6bcd217fa8a50ef5cb366c2d24392e3aa9a72</t>
+          <t>d1ca8d149f2fdfdf421d91b356058095f06de6d201c4ea2f3313f6c53e4af65f</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ТЕНЕВО СОЛАР ТЕХНОЛОДЖИС ЕАД</t>
+          <t>КАД-ПРОЕКТ ЕООД</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>206511621</t>
+          <t>101747052</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Тенево Солар"</t>
+          <t>ФтЕЦ "Златарица - 5"</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Ямбол</t>
+          <t>Велико Търново</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Тунджа</t>
+          <t>Златарица</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Тенево</t>
+          <t>Златарица</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>72240</t>
+          <t>30962</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>228.1</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>21.05.2026</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>11.06.2025</t>
-        </is>
-      </c>
+          <t>01.07.2026</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
@@ -4730,64 +4754,64 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>5112c5e02be5e596a8aa449da864564c6de7cf9541a801e8a13a7c192d0ca3aa</t>
+          <t>6c4f1030e5a53db717c87be3f790c9ff1f508921fd3da91b9e465036a91d7894</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ЮИДП ДП ТП ДЛС НЕСЕБЪР</t>
+          <t>МОНОЛИТ-21 - АНДОНОВ И ЗАХОВ ООД</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2016176540172</t>
+          <t>101732851</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ФтЕЦ "ТП Държавно ловно стопанство - Несебър"</t>
+          <t>ФтЕЦ "Монолит 21 Петрич"</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Бургас</t>
+          <t>Благоевград</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Несебър</t>
+          <t>Петрич</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Несебър</t>
+          <t>Петрич</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>51500</t>
+          <t>56126</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>0.0297</t>
+          <t>0.99953</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>25.09.2025</t>
+          <t>06.07.2026</t>
         </is>
       </c>
       <c r="J63" t="inlineStr"/>
@@ -4800,64 +4824,64 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>e2503d43f95f957800777cf5db6b3d093ec5723ed0383c2d02a8f12a2dba68d6</t>
+          <t>0f183f477ed77d36c5a0221e6c8712227f5dac8c478b28bd6743c806316883ab</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ИМПЕКС 2004 ЕООД</t>
+          <t>Пи Ви Парк Сандански ООД</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>206539476</t>
+          <t>206257992</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Импекс - Сливен 2"</t>
+          <t>ФтЕЦ "Пи Ви парк Сандански"</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Сливен</t>
+          <t>Благоевград</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Сливен</t>
+          <t>Сандански</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Сливен</t>
+          <t>Дебрене</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>67338</t>
+          <t>20345</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>0.199</t>
+          <t>2.916</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>12.11.2025</t>
+          <t>11.06.2025</t>
         </is>
       </c>
       <c r="J64" t="inlineStr"/>
@@ -4870,60 +4894,64 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>c3bf6f0366075934a8df5e36a640f26e45cca90e893feae55d863467e221581e</t>
+          <t>b28a883823dbcf2de28f4522d7527a755db94ccd76557eb17c74316e5a2e9720</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Камен Димитров Шишков</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr"/>
+          <t>Пи Ви ЕСКО ООД</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>206291187</t>
+        </is>
+      </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Павел - 1"</t>
+          <t>ФтЕЦ "Пи Ви Еско"</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Велико Търново</t>
+          <t>Благоевград</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Полски Тръмбеш</t>
+          <t>Сандански</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Павел</t>
+          <t>Джигурово</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>55018</t>
+          <t>20780</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>4.15584</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>24.10.2025</t>
+          <t>13.10.2025</t>
         </is>
       </c>
       <c r="J65" t="inlineStr"/>
@@ -4936,64 +4964,64 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>8d3b6b18a0d4f7cb6e70a229da7f150742fcbdd9289c0ef5d0b27a495c7e9a94</t>
+          <t>74bfc7ab2df35d7e47476d90f07e44112cee7df088beb2abee6072cc4ad7a647</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ЕС ПИ ЕНЕРДЖИ ЕНД УОТЪР ООД</t>
+          <t>ЦИРКОН ЕООД</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>207180791</t>
+          <t>829095157</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Ес Пи Енерджи Енд Уотър - Неделево"</t>
+          <t>ФтЕЦ "Циркон"</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Пловдив</t>
+          <t>Благоевград</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Съединение</t>
+          <t>Петрич</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Неделево</t>
+          <t>Кърналово</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>51305</t>
+          <t>40912</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>0.029945</t>
+          <t>0.21465</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>22.07.2025</t>
+          <t>16.06.2026</t>
         </is>
       </c>
       <c r="J66" t="inlineStr"/>
@@ -5006,64 +5034,64 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>30fd97c228589b95a9912e5d3490ebd90ce3afc00336989ba9a01f494b6bad0b</t>
+          <t>60ebc63763024f8a2b9df0de01dea01acd5af889310dbec577d48ffe11ef5818</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ТЕХНОКА СЕРВИЗ ЕООД</t>
+          <t>Пи Ви Лад ООД</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>201737041</t>
+          <t>206323756</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ФтЕЦ "ГИД Пауър -Жребино</t>
+          <t>ФтЕЦ "Пи Ви Лад"</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Ямбол</t>
+          <t>Благоевград</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Елхово</t>
+          <t>Сандански</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Жребино</t>
+          <t>Джигурово</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>29516</t>
+          <t>20780</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>0.09976</t>
+          <t>2.997</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>01.03.2026</t>
+          <t>14.10.2025</t>
         </is>
       </c>
       <c r="J67" t="inlineStr"/>
@@ -5076,64 +5104,64 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>3624a0bb40522c5ca41ed99bc5d4e7be9af2c996ca56151d09603ca7c881b870</t>
+          <t>711827d42eea8c4d6320edb791afe2bd25164a7684b357e8bcdc2d6e5665b261</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ХИДРО СИСТЕМИ МАРИЦА ЕООД</t>
+          <t>ДЖОДИ ЕНЕРДЖИ ЕООД</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>205891211</t>
+          <t>205879629</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ФтЕЦ "ММ Смарт Енерджи - Първомай"</t>
+          <t>ФТЕЦ"ХАТАНГА 3 ДРАЖЕВО"</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Пловдив</t>
+          <t>Ямбол</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Първомай</t>
+          <t>Тунджа</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Първомай</t>
+          <t>Дражево</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>59080</t>
+          <t>23501</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>17.09.2025</t>
+          <t>18.08.2026</t>
         </is>
       </c>
       <c r="J68" t="inlineStr"/>
@@ -5146,64 +5174,64 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>fa5f8869fe17b4957fb5bac392e24a45361e8b07a1b7ea92a27e3a97b15c8ac9</t>
+          <t>f1ff1c0ec42a6d2352391bd73a22999cd5755ad9b2083f50429147290f5fd2c3</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>"ГеоСоларити" ЕООД</t>
+          <t>ДЖОДИ ЕНЕРДЖИ ЕООД</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>206682271</t>
+          <t>205879629</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Тутракан - 3"</t>
+          <t>ФтЕЦ "Джоди Енерджи - Камен Връх УПИ I-228"</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Силистра</t>
+          <t>Ямбол</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Тутракан</t>
+          <t>Болярово</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Тутракан</t>
+          <t>Камен връх</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>73496</t>
+          <t>35756</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>0.06985</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>16.12.2025</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="J69" t="inlineStr"/>
@@ -5216,64 +5244,64 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>f89dd98cd457fc609d21fd961664f20f956d39fe5b8f4483711f996cfab9dc93</t>
+          <t>c6a0e4f2450987ac3fda327b38302ee3436d0be73e055a07c102970996be7333</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ТОДОР ДАМЯНОВ - МД ООД</t>
+          <t>СЪН ТЕХНОЛОДЖИ 3 ЕООД</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>104536480</t>
+          <t>206935194</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Велико Търново - Стоян Коледаров"</t>
+          <t>ФтЕЦ "Ряхово - 4"</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Велико Търново</t>
+          <t>Русе</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Велико Търново</t>
+          <t>Сливо поле</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Велико Търново</t>
+          <t>Ряхово</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>10447</t>
+          <t>63668</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>2.9606</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>12.09.2024</t>
+          <t>05.11.2025</t>
         </is>
       </c>
       <c r="J70" t="inlineStr"/>
@@ -5286,64 +5314,64 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>2bab61a0e424beb6edabaef84783e22390eea7b6f3a3f40cb881976a1f2624b0</t>
+          <t>41e3799fe3e441e82c7d4bbb81c5c6b0c017158cdaf982225acfa7f940d22ed9</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ТОДОР ДАМЯНОВ - МД ООД</t>
+          <t>СЪН ТЕХНОЛОДЖИ 1 ЕООД</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>104536480</t>
+          <t>206716979</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Лясковец - Оборище - 6"</t>
+          <t>ФтЕЦ "Осмар - 1"</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Велико Търново</t>
+          <t>Шумен</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Лясковец</t>
+          <t>Велики Преслав</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Лясковец</t>
+          <t>Осмар</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>44793</t>
+          <t>54273</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.98686</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>05.03.2026</t>
+          <t>26.07.2025</t>
         </is>
       </c>
       <c r="J71" t="inlineStr"/>
@@ -5356,64 +5384,64 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>ab7bdfd85a1a3ecb32bf9c00dd45ebdf2e60a16d363dcc79b87efd50e817f4ec</t>
+          <t>65ef609f4a3a648a4940de78c5862216fff22671b28cd495fa9f03d555984435</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>БОЙЧО ОГНЯНОВ 1 ООД</t>
+          <t>Тиера дел Сол 002 ЕООД</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>113549797</t>
+          <t>206691733</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Уоу маркет"</t>
+          <t>ФтЕЦ "Лозница - Разград - 2"</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Перник</t>
+          <t>Разград</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Радомир</t>
+          <t>Лозница</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Радомир</t>
+          <t>Лозница</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>61577</t>
+          <t>44166</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>4.17088</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>24.06.2026</t>
+          <t>29.11.2025</t>
         </is>
       </c>
       <c r="J72" t="inlineStr"/>
@@ -5426,64 +5454,64 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>b7f72136ecc9a449e96321a29175435992501d4e8ef61d5938edfc896137d9af</t>
+          <t>d5a63e28232975a549a0b4b91ce242464fa4062a29c3af5973ca00f04dacb1d1</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ЕЕ ИНВЕСТ ВЪЛЧИ ДОЛ ЕООД</t>
+          <t>Тиера дел Сол 002 ЕООД</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>206949009</t>
+          <t>206691733</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Вълчи дол - 4"</t>
+          <t>ФтЕЦ "Исперих - 10"</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Варна</t>
+          <t>Разград</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Вълчи дол</t>
+          <t>Исперих</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Вълчи дол</t>
+          <t>Исперих</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>12574</t>
+          <t>32874</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>5.95056</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>10.06.2026</t>
+          <t>27.01.2026</t>
         </is>
       </c>
       <c r="J73" t="inlineStr"/>
@@ -5496,64 +5524,64 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>97f1269b2072830e2f27fd30b0d9e7c7543718c2d9359e2ed4d85e9536265a5a</t>
+          <t>b817faa3434807e71b3908188293ce631778aa6812d402004923a1a83b433b1d</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ИНКОМС-ИНСТРУМЕНТИ И МЕХАНИКА АД</t>
+          <t>СЪНИ ЛЕНД 003 ЕООД</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>121110956</t>
+          <t>206691815</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ФтЕЦ Инкомс инструменти и механика</t>
+          <t>ФтЕЦ "Ястребово"</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>София-град</t>
+          <t>Русе</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Столична</t>
+          <t>Русе</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>София</t>
+          <t>Ястребово</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>68134</t>
+          <t>87700</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>2.55024</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>20.05.2026</t>
+          <t>21.10.2025</t>
         </is>
       </c>
       <c r="J74" t="inlineStr"/>
@@ -5566,64 +5594,64 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>6f18274456bbedb63ca8fa3ca610bf66d43bfe14f81b5cc8d34283685fd5e546</t>
+          <t>fc3947914d0e76d28f86fc7ef2996cccc45ea3f81a680b72ee04d994bceff85f</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Солар Еко КД ООД</t>
+          <t>СЪНИ ЛЕНД 003 ЕООД</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>206715312</t>
+          <t>206691815</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Суворово - 2"</t>
+          <t>ФтЕЦ "Ряхово - 5"</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Варна</t>
+          <t>Русе</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Суворово</t>
+          <t>Сливо поле</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Суворово</t>
+          <t>Ряхово</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>70175</t>
+          <t>63668</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>0.15865</t>
+          <t>5.95056</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>16.06.2026</t>
+          <t>06.11.2025</t>
         </is>
       </c>
       <c r="J75" t="inlineStr"/>
@@ -5636,60 +5664,64 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>92764fc97a8e66004cffa7a3f5b487d21567b1b764c5413d0eba52c8f8010dcd</t>
+          <t>31a597f6f193bd805965f93e803286677e3bb5d9f3cedd79d4dd781bc81d6d79</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Екатерина Дянкова Андреева</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr"/>
+          <t>СЪНИ ЛЕНД 003 ЕООД</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>206691815</t>
+        </is>
+      </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Екатерина Андреева - Раклица 1"</t>
+          <t>ФтЕЦ "Ценово - Стопански двор - 1"</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Бургас</t>
+          <t>Русе</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Карнобат</t>
+          <t>Ценово</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Раклица</t>
+          <t>Ценово</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>62027</t>
+          <t>78361</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>0.06042</t>
+          <t>2.295</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>29.05.2026</t>
+          <t>23.12.2025</t>
         </is>
       </c>
       <c r="J76" t="inlineStr"/>
@@ -5702,64 +5734,64 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>9984aac76f5bf69fadc7346485202585853ca5ec7ad7ca595467897befe6ad3c</t>
+          <t>a85dd97139da5b48edd6495f1b66db7c3d941e227dd02f09a428031f5b47d2d2</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Кооперация ЗК БАТА</t>
+          <t>КРАМОР ЕООД</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>812176576</t>
+          <t>131376699</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ФтЕЦ "ЗК Бата - Бата"</t>
+          <t>ФтЕЦ "Крамор 9"</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Бургас</t>
+          <t>Плевен</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Поморие</t>
+          <t>Червен бряг</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Бата</t>
+          <t>Чомаковци</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2810</t>
+          <t>81551</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>0.1988</t>
+          <t>0.029975</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>10.10.2024</t>
+          <t>14.05.2026</t>
         </is>
       </c>
       <c r="J77" t="inlineStr"/>
@@ -5772,64 +5804,64 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>8550ea3add80eb2ae6a3d3c35ecc3cfb5d9ac68afd129e4be6970c73a34e01a8</t>
+          <t>68fb18337279bdb22f518940258556d24db6105caa7bd96f84ff66f3775dc910</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>М.К.Р. ЕООД</t>
+          <t>ЕНЕРГО ИНВЕСТ СЕВЕР ООД</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>128621055</t>
+          <t>206818796</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ФтЕЦ "Ямбол - М.К.Р."</t>
+          <t>ФтЕЦ "Пиргово - Стара планина"</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Ямбол</t>
+          <t>Русе</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Ямбол</t>
+          <t>Иваново</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ямбол</t>
+          <t>Пиргово</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>87374</t>
+          <t>56397</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>0.0297</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>13.09.2025</t>
+          <t>12.12.2025</t>
         </is>
       </c>
       <c r="J78" t="inlineStr"/>
@@ -5842,1899 +5874,17 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>2c052790afae4e8bf4b4530fdb67755e92076dac2f9550b592b59866804bf7ba</t>
+          <t>b3367e3e177f4a89b6b991c024ce2b268f5b94ea6e2882c74f98135e408de9e0</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>2026-09-01T09:45:04+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>ГАРАНТ - Б ЕООД</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>119616950</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>ФтЕЦ "Гарант Б - Сливен 1"</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>Сливен</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>Сливен</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Сливен</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>67338</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>0.089835</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>13.03.2026</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>Слънчева енергия</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>906f6778f37ebd0862ac416d7821b660d066c5be4d8f33912ae7fa64c7467945</t>
-        </is>
-      </c>
-      <c r="O79" t="inlineStr">
-        <is>
-          <t>2026-09-01T09:45:04+03:00</t>
-        </is>
-      </c>
-      <c r="P79" t="inlineStr">
-        <is>
-          <t>2026-09-01T09:45:04+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>ЕВАЛДИ ЕООД</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>204890996</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>ФтЕЦ "Евалди - Руманя"</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Стара Загора</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>Стара Загора</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Руманя</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>63301</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>18.05.2026</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>Слънчева енергия</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>a4b8a8caa15917b24a977a909a92d59d971938d5e3f5d66bfeb656a11065b479</t>
-        </is>
-      </c>
-      <c r="O80" t="inlineStr">
-        <is>
-          <t>2026-09-01T09:45:04+03:00</t>
-        </is>
-      </c>
-      <c r="P80" t="inlineStr">
-        <is>
-          <t>2026-09-01T09:45:04+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>ПВ АЛИАНЦ ООД</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>205373286</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>ФтЕЦ "ПВ Алианц - Държава 4"</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Стара Загора</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Чирпан</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Държава</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>24623</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>0.09975</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>04.06.2026</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>Слънчева енергия</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>90272c918ba7d1fefb6d671b476665e3a5c71cffa448b51dced0766e22502693</t>
-        </is>
-      </c>
-      <c r="O81" t="inlineStr">
-        <is>
-          <t>2026-09-01T09:45:04+03:00</t>
-        </is>
-      </c>
-      <c r="P81" t="inlineStr">
-        <is>
-          <t>2026-09-01T09:45:04+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>СОЛАР ЦЕНТЪР ГРУП ЕООД</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>208666853</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>ФтЕЦ "Тракер Венци"</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Перник</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>Брезник</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Конска</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>41126</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>07.10.2025</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>Слънчева енергия</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>ec2226165e1dd9c2e687e251ab21570cd45beca73e1ac0a9dc4baa23cf4c2b07</t>
-        </is>
-      </c>
-      <c r="O82" t="inlineStr">
-        <is>
-          <t>2026-09-01T09:45:04+03:00</t>
-        </is>
-      </c>
-      <c r="P82" t="inlineStr">
-        <is>
-          <t>2026-09-01T09:45:04+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Даниел Георгиев Петков</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr"/>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>ФтЕЦ Даниел Петков -Шивачево</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>Сливен</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>Твърдица</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Шивачево</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>15944</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>0.0297</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>28.07.2026</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>Слънчева енергия</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>8f4c34e7c8a8f4b7933dd46dd4cab1dbe643862e511d907bd8b97e8e538a0169</t>
-        </is>
-      </c>
-      <c r="O83" t="inlineStr">
-        <is>
-          <t>2026-09-01T09:45:04+03:00</t>
-        </is>
-      </c>
-      <c r="P83" t="inlineStr">
-        <is>
-          <t>2026-09-01T09:45:04+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Волток Мега ООД</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>204882825</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>ФтЕЦ "Бяла - Русе - Чавдар войвода"</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>Русе</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>Бяла</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Бяла</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>7603</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>15.06.2026</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>Слънчева енергия</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>9c77558e1c928a78cf7ffb7aa88384a850c6f4eb966a406bc6eba8b948dfa452</t>
-        </is>
-      </c>
-      <c r="O84" t="inlineStr">
-        <is>
-          <t>2026-09-01T09:45:04+03:00</t>
-        </is>
-      </c>
-      <c r="P84" t="inlineStr">
-        <is>
-          <t>2026-09-01T09:45:04+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Карлово Солар Парк 2022 ЕООД</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>206796638</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>ФтЕЦ "Ведраре Солар"</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Пловдив</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>Карлово</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Ведраре</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>10291</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>87.877</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>10.06.2026</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>Слънчева енергия</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>7ad1b9e48a8387560888067d0764cb320d75b9ac3a2433000a23ec20ac3e6f05</t>
-        </is>
-      </c>
-      <c r="O85" t="inlineStr">
-        <is>
-          <t>2026-09-01T09:45:04+03:00</t>
-        </is>
-      </c>
-      <c r="P85" t="inlineStr">
-        <is>
-          <t>2026-09-01T09:45:04+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Диамант 2023 ЕООД</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>207215712</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>ФтЕЦ "Диамант 2023"</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>Враца</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>Мездра</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Мездра</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>47714</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>21.10.2025</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>Слънчева енергия</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>2da1e50adbbd03791d9e6ca76130c2cd20b33aacbec6ceb89ecaff8109d2fa01</t>
-        </is>
-      </c>
-      <c r="O86" t="inlineStr">
-        <is>
-          <t>2026-09-01T09:45:04+03:00</t>
-        </is>
-      </c>
-      <c r="P86" t="inlineStr">
-        <is>
-          <t>2026-09-01T09:45:04+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>ДЕЯН ВАН КОВ ЕООД</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>200000178</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>ФтЕЦ "Капитановци 2"</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>Видин</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>Видин</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Капитановци</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>36141</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>0.09974</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>17.07.2026</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>Слънчева енергия</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t>2726b548f37f2de31d98c8cf8eb49323579bc169c84bf4b13f3b80ae44a8c66d</t>
-        </is>
-      </c>
-      <c r="O87" t="inlineStr">
-        <is>
-          <t>2026-09-01T09:45:04+03:00</t>
-        </is>
-      </c>
-      <c r="P87" t="inlineStr">
-        <is>
-          <t>2026-09-01T09:45:04+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>СИСТЕМЕН АНАЛИЗ ООД</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>130992599</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>ФтЕЦ "Системен Анализ - Житница 2"</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>Пловдив</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>Калояново</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>Житница</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>29475</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>01.07.2026</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>Слънчева енергия</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t>4b02c1b2dba0d73d25d71893bb08101bcb7be4a0c8f42e35889f3ea2d951c557</t>
-        </is>
-      </c>
-      <c r="O88" t="inlineStr">
-        <is>
-          <t>2026-09-01T09:45:04+03:00</t>
-        </is>
-      </c>
-      <c r="P88" t="inlineStr">
-        <is>
-          <t>2026-09-01T09:45:04+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>ДЖОДИ ЕНЕРДЖИ ЕООД</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>205879629</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>ФтЕЦ "Джоди Енерджи - Синапово"</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>Хасково</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>Тополовград</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Синапово</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>66487</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>0.1298</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>16.07.2026</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>Слънчева енергия</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr">
-        <is>
-          <t>7a4f01f831280118730fbd9e2a8d44c37234157f8b31daac966c7cdb8a8d7cbb</t>
-        </is>
-      </c>
-      <c r="O89" t="inlineStr">
-        <is>
-          <t>2026-09-01T09:45:04+03:00</t>
-        </is>
-      </c>
-      <c r="P89" t="inlineStr">
-        <is>
-          <t>2026-09-01T09:45:04+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>ГАЛАКСИ ИНТЕРНЕШЪНЪЛ ООД</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>200590688</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>ФтЕЦ "Галакси Интернешънъл - Васил Левски"</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>Пловдив</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>Карлово</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Васил Левски</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>10207</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>0.18768</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>15.07.2026</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>Слънчева енергия</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr">
-        <is>
-          <t>b0dc2ef8836643a05075581bb0f28dbba07cf2ed834747e844f1d78f13ef5025</t>
-        </is>
-      </c>
-      <c r="O90" t="inlineStr">
-        <is>
-          <t>2026-09-01T09:45:04+03:00</t>
-        </is>
-      </c>
-      <c r="P90" t="inlineStr">
-        <is>
-          <t>2026-09-01T09:45:04+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>„ХОРИЗОНТ – ИВАНОВ” ЕООД</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>824121242</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>ФтЕЦ" Хоризонт Иванов "</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>Плевен</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>Плевен</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Плевен</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>56722</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>0.0597</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>10.08.2026</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>Слънчева енергия</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr">
-        <is>
-          <t>448715520387ea5962b32f6c4facc8214f7c898083f93845ec7894fd938a305f</t>
-        </is>
-      </c>
-      <c r="O91" t="inlineStr">
-        <is>
-          <t>2026-09-01T09:45:04+03:00</t>
-        </is>
-      </c>
-      <c r="P91" t="inlineStr">
-        <is>
-          <t>2026-09-01T09:45:04+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>РОКИ - 80 ЕООД</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>206188017</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>ФтЕЦ "Роки 4"</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>Плевен</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>Долна Митрополия</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Тръстеник</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>73359</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>26.06.2026</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>Слънчева енергия</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr">
-        <is>
-          <t>2329ba378d5870ecf9ad6155c6ae9d86c2e55e17e71b01942d59eb341426df44</t>
-        </is>
-      </c>
-      <c r="O92" t="inlineStr">
-        <is>
-          <t>2026-09-01T09:45:04+03:00</t>
-        </is>
-      </c>
-      <c r="P92" t="inlineStr">
-        <is>
-          <t>2026-09-01T09:45:04+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>РОКИ - 80 ЕООД</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>206188017</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>ФтЕЦ "Роки 5"</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>Плевен</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Долна Митрополия</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Тръстеник</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>73359</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>26.06.2026</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>Слънчева енергия</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr">
-        <is>
-          <t>d29883280650b4defcd765d0dea90a6d0ab31a996f8bd22b5158d72bb038b92a</t>
-        </is>
-      </c>
-      <c r="O93" t="inlineStr">
-        <is>
-          <t>2026-09-01T09:45:04+03:00</t>
-        </is>
-      </c>
-      <c r="P93" t="inlineStr">
-        <is>
-          <t>2026-09-01T09:45:04+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>НП Минкови ЕООД</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>207219493</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>ФтЕЦ "НП Минкови - Граф Игнатиево"</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>Пловдив</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>Марица</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Граф Игнатиево</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>17806</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>0.46864</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>08.07.2026</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>Слънчева енергия</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr">
-        <is>
-          <t>9ff036fadac5e645493f5bf4a07e5c5a195e3f8973b7a148dc58c6b575667bce</t>
-        </is>
-      </c>
-      <c r="O94" t="inlineStr">
-        <is>
-          <t>2026-09-01T09:45:04+03:00</t>
-        </is>
-      </c>
-      <c r="P94" t="inlineStr">
-        <is>
-          <t>2026-09-01T09:45:04+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>АВИС ИНЖЕНЕРИНГ ЕООД</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>115011904</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>ФтЕЦ "Авис Инженеринг - Пловдив"</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Пловдив</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>Пловдив</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Пловдив</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>56784</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>0.13978</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>11.05.2026</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>Слънчева енергия</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr">
-        <is>
-          <t>8aa1774e85b995916c200deffec1a39f20e636bccb7e55ca040090259346df51</t>
-        </is>
-      </c>
-      <c r="O95" t="inlineStr">
-        <is>
-          <t>2026-09-01T09:45:04+03:00</t>
-        </is>
-      </c>
-      <c r="P95" t="inlineStr">
-        <is>
-          <t>2026-09-01T09:45:04+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>СОЛАР ИИ ЕООД</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>207237616</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>ФтЕЦ "Екострой 2 - Раковски"</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>Пловдив</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>Раковски</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Раковски</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>62075</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>0.2065</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>15.07.2025</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>Слънчева енергия</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr">
-        <is>
-          <t>d50acb979857633959a0fb2c17b7a32387212f2d0e276ea325c0c21d455305f8</t>
-        </is>
-      </c>
-      <c r="O96" t="inlineStr">
-        <is>
-          <t>2026-09-01T09:45:04+03:00</t>
-        </is>
-      </c>
-      <c r="P96" t="inlineStr">
-        <is>
-          <t>2026-09-01T09:45:04+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Булсан Ямбол 1 ЕООД</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>206863649</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>ФтЕЦ "Булсан Ямбол 1 -Ямбол"</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>Ямбол</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>Ямбол</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Ямбол</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>87374</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>3.6</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>20.03.2025</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>Слънчева енергия</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr">
-        <is>
-          <t>264ab07176ed360fcb6e3b0a29df31d8f4bd5b3af12f1847361df3ffc48bef19</t>
-        </is>
-      </c>
-      <c r="O97" t="inlineStr">
-        <is>
-          <t>2026-09-01T09:45:04+03:00</t>
-        </is>
-      </c>
-      <c r="P97" t="inlineStr">
-        <is>
-          <t>2026-09-01T09:45:04+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Донатекс и Ко ЕООД</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>115107055</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>ФтЕЦ "Донатекс - Сушица"</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>Пловдив</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>Карлово</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Карлово</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>36498</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>3.0038</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>13.05.2026</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>Слънчева енергия</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr">
-        <is>
-          <t>c9e0c31e32c13db4b2903b3f83a43e6a22ce77d211c9a3635534d3eca06152be</t>
-        </is>
-      </c>
-      <c r="O98" t="inlineStr">
-        <is>
-          <t>2026-09-01T09:45:04+03:00</t>
-        </is>
-      </c>
-      <c r="P98" t="inlineStr">
-        <is>
-          <t>2026-09-01T09:45:04+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>МАЛЕНОВО СОЛАР ООД</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>200654831</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>ФтЕЦ "Маленово - Сливен 1"</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>Сливен</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>Сливен</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>Сливен</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>67338</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>0.1998</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>20.07.2026</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>Слънчева енергия</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr">
-        <is>
-          <t>6b854eaa4133f5494dea075656c968656ecbfffe57e0009f6b1d7bf83be340e2</t>
-        </is>
-      </c>
-      <c r="O99" t="inlineStr">
-        <is>
-          <t>2026-09-01T09:45:04+03:00</t>
-        </is>
-      </c>
-      <c r="P99" t="inlineStr">
-        <is>
-          <t>2026-09-01T09:45:04+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>ЗЕЙНЕЛ ХЮСЕИН БОБА</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr"/>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>ФтЕЦ "Чернолик - Черно Море - 1"</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>Силистра</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>Дулово</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>Чернолик</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>81150</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>0.015</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>29.10.2025</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>Слънчева енергия</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr">
-        <is>
-          <t>5d2e28cf0cf23f9f9b1accd010ee772cf89882dcda36c0979a76f1fe25f65bb8</t>
-        </is>
-      </c>
-      <c r="O100" t="inlineStr">
-        <is>
-          <t>2026-09-01T09:45:04+03:00</t>
-        </is>
-      </c>
-      <c r="P100" t="inlineStr">
-        <is>
-          <t>2026-09-01T09:45:04+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>"БИО ТРЕЕ" ЕООД</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>203774259</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>ФтЕЦ "Тутраканци - 6"</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>Варна</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>Провадия</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>Тутраканци</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>73506</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>12.06.2025</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>Слънчева енергия</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr">
-        <is>
-          <t>98332515d297a2c5f4f43fdf38393ef5cf2b493fd55860c636c060370c19d2bb</t>
-        </is>
-      </c>
-      <c r="O101" t="inlineStr">
-        <is>
-          <t>2026-09-01T09:45:04+03:00</t>
-        </is>
-      </c>
-      <c r="P101" t="inlineStr">
-        <is>
-          <t>2026-09-01T09:45:04+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>АЛЕКС - 2015 С ЕООД</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>206846920</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>ФтЕЦ "Живодар Стойчев - Гълъбово 1"</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>Стара Загора</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>Гълъбово</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>Гълъбово</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>18280</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>0.14762</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>01.04.2026</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>Слънчева енергия</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr">
-        <is>
-          <t>5ee9fea8e97c18ed80a754d3f51f226821e239b8cdf94f5ca83b6dd9a0933655</t>
-        </is>
-      </c>
-      <c r="O102" t="inlineStr">
-        <is>
-          <t>2026-09-01T09:45:04+03:00</t>
-        </is>
-      </c>
-      <c r="P102" t="inlineStr">
-        <is>
-          <t>2026-09-01T09:45:04+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>"ФЕЛТИН"ООД</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>207175997</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>ФтЕЦ "Фелтин Гъмзово"</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>Видин</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>Брегово</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>Гъмзово</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>18304</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>0.49996</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>07.07.2026</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>Слънчева енергия</t>
-        </is>
-      </c>
-      <c r="N103" t="inlineStr">
-        <is>
-          <t>9334bb06ece1236f48e321d60b273dff10bbdf312f25f2834448fa7fb6b4a9a3</t>
-        </is>
-      </c>
-      <c r="O103" t="inlineStr">
-        <is>
-          <t>2026-09-01T09:45:04+03:00</t>
-        </is>
-      </c>
-      <c r="P103" t="inlineStr">
-        <is>
-          <t>2026-09-01T09:45:04+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>ЗП ТОНЧО НИКОЛОВ ДРАГНЕВ</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>102907086</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>ФтЕЦ "Тончо Драгнев - Славянци 5"</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>Бургас</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>Сунгурларе</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>Славянци</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>67115</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>0.08</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>03.07.2026</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>Слънчева енергия</t>
-        </is>
-      </c>
-      <c r="N104" t="inlineStr">
-        <is>
-          <t>fa8782ac2fe781a6782b778c0577b3afece8ab8a4ff2ae50bbe12a25e70170bd</t>
-        </is>
-      </c>
-      <c r="O104" t="inlineStr">
-        <is>
-          <t>2026-09-01T09:45:04+03:00</t>
-        </is>
-      </c>
-      <c r="P104" t="inlineStr">
-        <is>
-          <t>2026-09-01T09:45:04+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Фреш Тейст АД</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>203479173</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>ФтЕЦ "Варна - Владислав Варненчик -16"</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>Варна</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>Варна</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>Варна</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>10135</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>0.33385</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>17.07.2026</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>Слънчева енергия</t>
-        </is>
-      </c>
-      <c r="N105" t="inlineStr">
-        <is>
-          <t>cbe52d5e7ef286342729ca26c36fb0170af3311097e87bbb025281b0e2fb20ce</t>
-        </is>
-      </c>
-      <c r="O105" t="inlineStr">
-        <is>
-          <t>2026-09-01T09:45:04+03:00</t>
-        </is>
-      </c>
-      <c r="P105" t="inlineStr">
-        <is>
-          <t>2026-09-01T09:45:04+03:00</t>
+          <t>2026-10-01T09:48:54+03:00</t>
         </is>
       </c>
     </row>
